--- a/Data/OptimizedTableExample.xlsx
+++ b/Data/OptimizedTableExample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E0803344\OneDrive - Eaton\Documents\JavierCamacho\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82784B83-AFA2-489C-B481-EE525A4203A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB725349-F328-4783-A5A0-02F0228D3167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{534B40DD-534D-4077-B159-601DF4A6319C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11090" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11099" uniqueCount="45">
   <si>
     <t>Line Type</t>
   </si>
@@ -170,14 +170,32 @@
   <si>
     <t>OR:Ples_2-6</t>
   </si>
+  <si>
+    <t>Or X</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -276,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -293,6 +311,8 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40F5F76-32D5-4517-AC84-026EF2B779AF}">
-  <dimension ref="B2:Y702"/>
+  <dimension ref="B2:Y703"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.5703125" customWidth="1"/>
@@ -858,42 +878,46 @@
       <c r="X8" s="6"/>
       <c r="Y8" s="10"/>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
+    <row r="9" spans="2:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="B9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="11">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>22</v>
+      <c r="D9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="10"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="10"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
@@ -909,7 +933,7 @@
         <v>17</v>
       </c>
       <c r="F10" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>18</v>
@@ -923,6 +947,14 @@
       <c r="J10" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="10"/>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
@@ -938,7 +970,7 @@
         <v>17</v>
       </c>
       <c r="F11" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>18</v>
@@ -967,7 +999,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>18</v>
@@ -996,7 +1028,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>18</v>
@@ -1025,7 +1057,7 @@
         <v>17</v>
       </c>
       <c r="F14" s="11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>18</v>
@@ -1036,8 +1068,8 @@
       <c r="I14" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>23</v>
+      <c r="J14" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.25">
@@ -1054,7 +1086,7 @@
         <v>17</v>
       </c>
       <c r="F15" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>18</v>
@@ -1083,7 +1115,7 @@
         <v>17</v>
       </c>
       <c r="F16" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>18</v>
@@ -1112,7 +1144,7 @@
         <v>17</v>
       </c>
       <c r="F17" s="11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>18</v>
@@ -1141,7 +1173,7 @@
         <v>17</v>
       </c>
       <c r="F18" s="11">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>18</v>
@@ -1150,10 +1182,10 @@
         <v>17</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
@@ -1170,7 +1202,7 @@
         <v>17</v>
       </c>
       <c r="F19" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>18</v>
@@ -1199,7 +1231,7 @@
         <v>17</v>
       </c>
       <c r="F20" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>18</v>
@@ -1228,7 +1260,7 @@
         <v>17</v>
       </c>
       <c r="F21" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>18</v>
@@ -1257,7 +1289,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>18</v>
@@ -1286,7 +1318,7 @@
         <v>17</v>
       </c>
       <c r="F23" s="11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>18</v>
@@ -1297,8 +1329,8 @@
       <c r="I23" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="12" t="s">
-        <v>23</v>
+      <c r="J23" s="13" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
@@ -1315,7 +1347,7 @@
         <v>17</v>
       </c>
       <c r="F24" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>18</v>
@@ -1344,7 +1376,7 @@
         <v>17</v>
       </c>
       <c r="F25" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>18</v>
@@ -1373,7 +1405,7 @@
         <v>17</v>
       </c>
       <c r="F26" s="11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>18</v>
@@ -1389,32 +1421,32 @@
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-      <c r="G27" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" t="s">
-        <v>22</v>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="11">
+        <v>20</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
@@ -1431,7 +1463,7 @@
         <v>17</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" t="s">
         <v>18</v>
@@ -1460,7 +1492,7 @@
         <v>17</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="s">
         <v>18</v>
@@ -1489,7 +1521,7 @@
         <v>17</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" t="s">
         <v>18</v>
@@ -1518,7 +1550,7 @@
         <v>17</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" t="s">
         <v>18</v>
@@ -1547,7 +1579,7 @@
         <v>17</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G32" t="s">
         <v>18</v>
@@ -1559,7 +1591,7 @@
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
@@ -1576,7 +1608,7 @@
         <v>17</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" t="s">
         <v>18</v>
@@ -1605,7 +1637,7 @@
         <v>17</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G34" t="s">
         <v>18</v>
@@ -1634,7 +1666,7 @@
         <v>17</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
@@ -1657,13 +1689,13 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G36" t="s">
         <v>18</v>
@@ -1672,10 +1704,10 @@
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
@@ -1692,7 +1724,7 @@
         <v>17</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
         <v>18</v>
@@ -1721,7 +1753,7 @@
         <v>17</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G38" t="s">
         <v>18</v>
@@ -1750,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="F39">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -1762,7 +1794,7 @@
         <v>19</v>
       </c>
       <c r="J39" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
@@ -1779,7 +1811,7 @@
         <v>17</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
         <v>18</v>
@@ -1788,10 +1820,10 @@
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
@@ -1808,7 +1840,7 @@
         <v>17</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" t="s">
         <v>18</v>
@@ -1837,7 +1869,7 @@
         <v>17</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="s">
         <v>18</v>
@@ -1866,7 +1898,7 @@
         <v>17</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G43" t="s">
         <v>18</v>
@@ -1895,7 +1927,7 @@
         <v>17</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G44" t="s">
         <v>18</v>
@@ -1907,7 +1939,7 @@
         <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
@@ -1924,7 +1956,7 @@
         <v>17</v>
       </c>
       <c r="F45">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G45" t="s">
         <v>18</v>
@@ -1936,7 +1968,7 @@
         <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
@@ -1953,7 +1985,7 @@
         <v>17</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
@@ -1982,7 +2014,7 @@
         <v>17</v>
       </c>
       <c r="F47">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G47" t="s">
         <v>18</v>
@@ -2011,7 +2043,7 @@
         <v>17</v>
       </c>
       <c r="F48">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G48" t="s">
         <v>18</v>
@@ -2040,7 +2072,7 @@
         <v>17</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G49" t="s">
         <v>18</v>
@@ -2049,10 +2081,10 @@
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
@@ -2069,7 +2101,7 @@
         <v>17</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" t="s">
         <v>18</v>
@@ -2098,7 +2130,7 @@
         <v>17</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" t="s">
         <v>18</v>
@@ -2127,7 +2159,7 @@
         <v>17</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G52" t="s">
         <v>18</v>
@@ -2156,7 +2188,7 @@
         <v>17</v>
       </c>
       <c r="F53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53" t="s">
         <v>18</v>
@@ -2168,7 +2200,7 @@
         <v>24</v>
       </c>
       <c r="J53" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
@@ -2185,7 +2217,7 @@
         <v>17</v>
       </c>
       <c r="F54">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G54" t="s">
         <v>18</v>
@@ -2197,7 +2229,7 @@
         <v>24</v>
       </c>
       <c r="J54" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
@@ -2214,7 +2246,7 @@
         <v>17</v>
       </c>
       <c r="F55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55" t="s">
         <v>18</v>
@@ -2243,7 +2275,7 @@
         <v>17</v>
       </c>
       <c r="F56">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G56" t="s">
         <v>18</v>
@@ -2272,7 +2304,7 @@
         <v>17</v>
       </c>
       <c r="F57">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G57" t="s">
         <v>18</v>
@@ -2301,7 +2333,7 @@
         <v>17</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G58" t="s">
         <v>18</v>
@@ -2310,10 +2342,10 @@
         <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
@@ -2330,7 +2362,7 @@
         <v>17</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" t="s">
         <v>18</v>
@@ -2359,7 +2391,7 @@
         <v>17</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G60" t="s">
         <v>18</v>
@@ -2388,7 +2420,7 @@
         <v>17</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G61" t="s">
         <v>18</v>
@@ -2417,7 +2449,7 @@
         <v>17</v>
       </c>
       <c r="F62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G62" t="s">
         <v>18</v>
@@ -2429,7 +2461,7 @@
         <v>25</v>
       </c>
       <c r="J62" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
@@ -2446,7 +2478,7 @@
         <v>17</v>
       </c>
       <c r="F63">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G63" t="s">
         <v>18</v>
@@ -2458,7 +2490,7 @@
         <v>25</v>
       </c>
       <c r="J63" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
@@ -2475,7 +2507,7 @@
         <v>17</v>
       </c>
       <c r="F64">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G64" t="s">
         <v>18</v>
@@ -2504,7 +2536,7 @@
         <v>17</v>
       </c>
       <c r="F65">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G65" t="s">
         <v>18</v>
@@ -2533,7 +2565,7 @@
         <v>17</v>
       </c>
       <c r="F66">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G66" t="s">
         <v>18</v>
@@ -2556,13 +2588,13 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
         <v>17</v>
       </c>
       <c r="F67">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G67" t="s">
         <v>18</v>
@@ -2571,10 +2603,10 @@
         <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
@@ -2591,7 +2623,7 @@
         <v>17</v>
       </c>
       <c r="F68">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G68" t="s">
         <v>18</v>
@@ -2620,7 +2652,7 @@
         <v>17</v>
       </c>
       <c r="F69">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G69" t="s">
         <v>18</v>
@@ -2649,7 +2681,7 @@
         <v>17</v>
       </c>
       <c r="F70">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G70" t="s">
         <v>18</v>
@@ -2661,7 +2693,7 @@
         <v>19</v>
       </c>
       <c r="J70" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
@@ -2678,7 +2710,7 @@
         <v>17</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G71" t="s">
         <v>18</v>
@@ -2687,10 +2719,10 @@
         <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J71" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.25">
@@ -2707,7 +2739,7 @@
         <v>17</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72" t="s">
         <v>18</v>
@@ -2736,7 +2768,7 @@
         <v>17</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G73" t="s">
         <v>18</v>
@@ -2765,7 +2797,7 @@
         <v>17</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G74" t="s">
         <v>18</v>
@@ -2794,7 +2826,7 @@
         <v>17</v>
       </c>
       <c r="F75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" t="s">
         <v>18</v>
@@ -2806,7 +2838,7 @@
         <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.25">
@@ -2823,7 +2855,7 @@
         <v>17</v>
       </c>
       <c r="F76">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G76" t="s">
         <v>18</v>
@@ -2835,7 +2867,7 @@
         <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.25">
@@ -2852,7 +2884,7 @@
         <v>17</v>
       </c>
       <c r="F77">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G77" t="s">
         <v>18</v>
@@ -2881,7 +2913,7 @@
         <v>17</v>
       </c>
       <c r="F78">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G78" t="s">
         <v>18</v>
@@ -2910,7 +2942,7 @@
         <v>17</v>
       </c>
       <c r="F79">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G79" t="s">
         <v>18</v>
@@ -2939,7 +2971,7 @@
         <v>17</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G80" t="s">
         <v>18</v>
@@ -2948,10 +2980,10 @@
         <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.25">
@@ -2968,7 +3000,7 @@
         <v>17</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81" t="s">
         <v>18</v>
@@ -2997,7 +3029,7 @@
         <v>17</v>
       </c>
       <c r="F82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82" t="s">
         <v>18</v>
@@ -3026,7 +3058,7 @@
         <v>17</v>
       </c>
       <c r="F83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83" t="s">
         <v>18</v>
@@ -3055,7 +3087,7 @@
         <v>17</v>
       </c>
       <c r="F84">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G84" t="s">
         <v>18</v>
@@ -3067,7 +3099,7 @@
         <v>24</v>
       </c>
       <c r="J84" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.25">
@@ -3084,7 +3116,7 @@
         <v>17</v>
       </c>
       <c r="F85">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G85" t="s">
         <v>18</v>
@@ -3096,7 +3128,7 @@
         <v>24</v>
       </c>
       <c r="J85" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.25">
@@ -3113,7 +3145,7 @@
         <v>17</v>
       </c>
       <c r="F86">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G86" t="s">
         <v>18</v>
@@ -3142,7 +3174,7 @@
         <v>17</v>
       </c>
       <c r="F87">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G87" t="s">
         <v>18</v>
@@ -3171,7 +3203,7 @@
         <v>17</v>
       </c>
       <c r="F88">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
         <v>18</v>
@@ -3200,7 +3232,7 @@
         <v>17</v>
       </c>
       <c r="F89">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G89" t="s">
         <v>18</v>
@@ -3209,10 +3241,10 @@
         <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J89" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.25">
@@ -3229,7 +3261,7 @@
         <v>17</v>
       </c>
       <c r="F90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" t="s">
         <v>18</v>
@@ -3258,7 +3290,7 @@
         <v>17</v>
       </c>
       <c r="F91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G91" t="s">
         <v>18</v>
@@ -3287,7 +3319,7 @@
         <v>17</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G92" t="s">
         <v>18</v>
@@ -3316,7 +3348,7 @@
         <v>17</v>
       </c>
       <c r="F93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G93" t="s">
         <v>18</v>
@@ -3328,7 +3360,7 @@
         <v>25</v>
       </c>
       <c r="J93" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.25">
@@ -3345,7 +3377,7 @@
         <v>17</v>
       </c>
       <c r="F94">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G94" t="s">
         <v>18</v>
@@ -3357,7 +3389,7 @@
         <v>25</v>
       </c>
       <c r="J94" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.25">
@@ -3374,7 +3406,7 @@
         <v>17</v>
       </c>
       <c r="F95">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G95" t="s">
         <v>18</v>
@@ -3403,7 +3435,7 @@
         <v>17</v>
       </c>
       <c r="F96">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G96" t="s">
         <v>18</v>
@@ -3432,7 +3464,7 @@
         <v>17</v>
       </c>
       <c r="F97">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G97" t="s">
         <v>18</v>
@@ -3452,16 +3484,16 @@
         <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E98" t="s">
         <v>17</v>
       </c>
       <c r="F98">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G98" t="s">
         <v>18</v>
@@ -3470,10 +3502,10 @@
         <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J98" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.25">
@@ -3490,7 +3522,7 @@
         <v>17</v>
       </c>
       <c r="F99">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G99" t="s">
         <v>18</v>
@@ -3519,7 +3551,7 @@
         <v>17</v>
       </c>
       <c r="F100">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G100" t="s">
         <v>18</v>
@@ -3548,7 +3580,7 @@
         <v>17</v>
       </c>
       <c r="F101">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G101" t="s">
         <v>18</v>
@@ -3577,7 +3609,7 @@
         <v>17</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G102" t="s">
         <v>18</v>
@@ -3586,10 +3618,10 @@
         <v>17</v>
       </c>
       <c r="I102" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J102" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.25">
@@ -3606,7 +3638,7 @@
         <v>17</v>
       </c>
       <c r="F103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G103" t="s">
         <v>18</v>
@@ -3635,7 +3667,7 @@
         <v>17</v>
       </c>
       <c r="F104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G104" t="s">
         <v>18</v>
@@ -3664,7 +3696,7 @@
         <v>17</v>
       </c>
       <c r="F105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G105" t="s">
         <v>18</v>
@@ -3676,7 +3708,7 @@
         <v>21</v>
       </c>
       <c r="J105" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.25">
@@ -3693,7 +3725,7 @@
         <v>17</v>
       </c>
       <c r="F106">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G106" t="s">
         <v>18</v>
@@ -3722,7 +3754,7 @@
         <v>17</v>
       </c>
       <c r="F107">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G107" t="s">
         <v>18</v>
@@ -3734,7 +3766,7 @@
         <v>21</v>
       </c>
       <c r="J107" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.25">
@@ -3751,7 +3783,7 @@
         <v>17</v>
       </c>
       <c r="F108">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G108" t="s">
         <v>18</v>
@@ -3780,7 +3812,7 @@
         <v>17</v>
       </c>
       <c r="F109">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G109" t="s">
         <v>18</v>
@@ -3809,7 +3841,7 @@
         <v>17</v>
       </c>
       <c r="F110">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G110" t="s">
         <v>18</v>
@@ -3821,7 +3853,7 @@
         <v>21</v>
       </c>
       <c r="J110" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.25">
@@ -3838,7 +3870,7 @@
         <v>17</v>
       </c>
       <c r="F111">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G111" t="s">
         <v>18</v>
@@ -3847,10 +3879,10 @@
         <v>17</v>
       </c>
       <c r="I111" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J111" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.25">
@@ -3867,7 +3899,7 @@
         <v>17</v>
       </c>
       <c r="F112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G112" t="s">
         <v>18</v>
@@ -3896,7 +3928,7 @@
         <v>17</v>
       </c>
       <c r="F113">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G113" t="s">
         <v>18</v>
@@ -3925,7 +3957,7 @@
         <v>17</v>
       </c>
       <c r="F114">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G114" t="s">
         <v>18</v>
@@ -3937,7 +3969,7 @@
         <v>24</v>
       </c>
       <c r="J114" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.25">
@@ -3954,7 +3986,7 @@
         <v>17</v>
       </c>
       <c r="F115">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G115" t="s">
         <v>18</v>
@@ -3983,7 +4015,7 @@
         <v>17</v>
       </c>
       <c r="F116">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G116" t="s">
         <v>18</v>
@@ -3995,7 +4027,7 @@
         <v>24</v>
       </c>
       <c r="J116" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.25">
@@ -4012,7 +4044,7 @@
         <v>17</v>
       </c>
       <c r="F117">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G117" t="s">
         <v>18</v>
@@ -4041,7 +4073,7 @@
         <v>17</v>
       </c>
       <c r="F118">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G118" t="s">
         <v>18</v>
@@ -4070,7 +4102,7 @@
         <v>17</v>
       </c>
       <c r="F119">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G119" t="s">
         <v>18</v>
@@ -4082,7 +4114,7 @@
         <v>24</v>
       </c>
       <c r="J119" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.25">
@@ -4099,7 +4131,7 @@
         <v>17</v>
       </c>
       <c r="F120">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G120" t="s">
         <v>18</v>
@@ -4108,10 +4140,10 @@
         <v>17</v>
       </c>
       <c r="I120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J120" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.25">
@@ -4128,7 +4160,7 @@
         <v>17</v>
       </c>
       <c r="F121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G121" t="s">
         <v>18</v>
@@ -4157,7 +4189,7 @@
         <v>17</v>
       </c>
       <c r="F122">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G122" t="s">
         <v>18</v>
@@ -4186,7 +4218,7 @@
         <v>17</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G123" t="s">
         <v>18</v>
@@ -4198,7 +4230,7 @@
         <v>25</v>
       </c>
       <c r="J123" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.25">
@@ -4215,7 +4247,7 @@
         <v>17</v>
       </c>
       <c r="F124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G124" t="s">
         <v>18</v>
@@ -4244,7 +4276,7 @@
         <v>17</v>
       </c>
       <c r="F125">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G125" t="s">
         <v>18</v>
@@ -4256,7 +4288,7 @@
         <v>25</v>
       </c>
       <c r="J125" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.25">
@@ -4273,7 +4305,7 @@
         <v>17</v>
       </c>
       <c r="F126">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G126" t="s">
         <v>18</v>
@@ -4302,7 +4334,7 @@
         <v>17</v>
       </c>
       <c r="F127">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G127" t="s">
         <v>18</v>
@@ -4331,7 +4363,7 @@
         <v>17</v>
       </c>
       <c r="F128">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G128" t="s">
         <v>18</v>
@@ -4343,7 +4375,7 @@
         <v>25</v>
       </c>
       <c r="J128" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.25">
@@ -4354,13 +4386,13 @@
         <v>30</v>
       </c>
       <c r="D129" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E129" t="s">
         <v>17</v>
       </c>
       <c r="F129">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G129" t="s">
         <v>18</v>
@@ -4369,10 +4401,10 @@
         <v>17</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J129" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.25">
@@ -4389,7 +4421,7 @@
         <v>17</v>
       </c>
       <c r="F130">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G130" t="s">
         <v>18</v>
@@ -4418,7 +4450,7 @@
         <v>17</v>
       </c>
       <c r="F131">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G131" t="s">
         <v>18</v>
@@ -4447,7 +4479,7 @@
         <v>17</v>
       </c>
       <c r="F132">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G132" t="s">
         <v>18</v>
@@ -4459,7 +4491,7 @@
         <v>19</v>
       </c>
       <c r="J132" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.25">
@@ -4476,7 +4508,7 @@
         <v>17</v>
       </c>
       <c r="F133">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G133" t="s">
         <v>18</v>
@@ -4485,10 +4517,10 @@
         <v>17</v>
       </c>
       <c r="I133" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J133" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.25">
@@ -4505,7 +4537,7 @@
         <v>17</v>
       </c>
       <c r="F134">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G134" t="s">
         <v>18</v>
@@ -4534,7 +4566,7 @@
         <v>17</v>
       </c>
       <c r="F135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G135" t="s">
         <v>18</v>
@@ -4563,7 +4595,7 @@
         <v>17</v>
       </c>
       <c r="F136">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G136" t="s">
         <v>18</v>
@@ -4592,7 +4624,7 @@
         <v>17</v>
       </c>
       <c r="F137">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G137" t="s">
         <v>18</v>
@@ -4621,7 +4653,7 @@
         <v>17</v>
       </c>
       <c r="F138">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G138" t="s">
         <v>18</v>
@@ -4633,7 +4665,7 @@
         <v>21</v>
       </c>
       <c r="J138" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.25">
@@ -4650,7 +4682,7 @@
         <v>17</v>
       </c>
       <c r="F139">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G139" t="s">
         <v>18</v>
@@ -4679,7 +4711,7 @@
         <v>17</v>
       </c>
       <c r="F140">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G140" t="s">
         <v>18</v>
@@ -4708,7 +4740,7 @@
         <v>17</v>
       </c>
       <c r="F141">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G141" t="s">
         <v>18</v>
@@ -4720,7 +4752,7 @@
         <v>21</v>
       </c>
       <c r="J141" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.25">
@@ -4737,7 +4769,7 @@
         <v>17</v>
       </c>
       <c r="F142">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G142" t="s">
         <v>18</v>
@@ -4746,10 +4778,10 @@
         <v>17</v>
       </c>
       <c r="I142" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J142" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" spans="2:10" x14ac:dyDescent="0.25">
@@ -4766,7 +4798,7 @@
         <v>17</v>
       </c>
       <c r="F143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G143" t="s">
         <v>18</v>
@@ -4795,7 +4827,7 @@
         <v>17</v>
       </c>
       <c r="F144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G144" t="s">
         <v>18</v>
@@ -4824,7 +4856,7 @@
         <v>17</v>
       </c>
       <c r="F145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G145" t="s">
         <v>18</v>
@@ -4853,7 +4885,7 @@
         <v>17</v>
       </c>
       <c r="F146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G146" t="s">
         <v>18</v>
@@ -4882,7 +4914,7 @@
         <v>17</v>
       </c>
       <c r="F147">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G147" t="s">
         <v>18</v>
@@ -4894,7 +4926,7 @@
         <v>24</v>
       </c>
       <c r="J147" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.25">
@@ -4911,7 +4943,7 @@
         <v>17</v>
       </c>
       <c r="F148">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G148" t="s">
         <v>18</v>
@@ -4940,7 +4972,7 @@
         <v>17</v>
       </c>
       <c r="F149">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G149" t="s">
         <v>18</v>
@@ -4969,7 +5001,7 @@
         <v>17</v>
       </c>
       <c r="F150">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G150" t="s">
         <v>18</v>
@@ -4981,7 +5013,7 @@
         <v>24</v>
       </c>
       <c r="J150" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.25">
@@ -4998,7 +5030,7 @@
         <v>17</v>
       </c>
       <c r="F151">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G151" t="s">
         <v>18</v>
@@ -5007,10 +5039,10 @@
         <v>17</v>
       </c>
       <c r="I151" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J151" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.25">
@@ -5027,7 +5059,7 @@
         <v>17</v>
       </c>
       <c r="F152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G152" t="s">
         <v>18</v>
@@ -5056,7 +5088,7 @@
         <v>17</v>
       </c>
       <c r="F153">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G153" t="s">
         <v>18</v>
@@ -5085,7 +5117,7 @@
         <v>17</v>
       </c>
       <c r="F154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G154" t="s">
         <v>18</v>
@@ -5114,7 +5146,7 @@
         <v>17</v>
       </c>
       <c r="F155">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G155" t="s">
         <v>18</v>
@@ -5143,7 +5175,7 @@
         <v>17</v>
       </c>
       <c r="F156">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G156" t="s">
         <v>18</v>
@@ -5155,7 +5187,7 @@
         <v>25</v>
       </c>
       <c r="J156" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157" spans="2:10" x14ac:dyDescent="0.25">
@@ -5172,7 +5204,7 @@
         <v>17</v>
       </c>
       <c r="F157">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G157" t="s">
         <v>18</v>
@@ -5201,7 +5233,7 @@
         <v>17</v>
       </c>
       <c r="F158">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G158" t="s">
         <v>18</v>
@@ -5230,7 +5262,7 @@
         <v>17</v>
       </c>
       <c r="F159">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G159" t="s">
         <v>18</v>
@@ -5242,7 +5274,7 @@
         <v>25</v>
       </c>
       <c r="J159" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="2:10" x14ac:dyDescent="0.25">
@@ -5253,13 +5285,13 @@
         <v>30</v>
       </c>
       <c r="D160" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E160" t="s">
         <v>17</v>
       </c>
       <c r="F160">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G160" t="s">
         <v>18</v>
@@ -5268,10 +5300,10 @@
         <v>17</v>
       </c>
       <c r="I160" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J160" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.25">
@@ -5288,7 +5320,7 @@
         <v>17</v>
       </c>
       <c r="F161">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G161" t="s">
         <v>18</v>
@@ -5317,7 +5349,7 @@
         <v>17</v>
       </c>
       <c r="F162">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G162" t="s">
         <v>18</v>
@@ -5346,7 +5378,7 @@
         <v>17</v>
       </c>
       <c r="F163">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G163" t="s">
         <v>18</v>
@@ -5358,7 +5390,7 @@
         <v>19</v>
       </c>
       <c r="J163" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.25">
@@ -5375,7 +5407,7 @@
         <v>17</v>
       </c>
       <c r="F164">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G164" t="s">
         <v>18</v>
@@ -5384,10 +5416,10 @@
         <v>17</v>
       </c>
       <c r="I164" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J164" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.25">
@@ -5404,7 +5436,7 @@
         <v>17</v>
       </c>
       <c r="F165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G165" t="s">
         <v>18</v>
@@ -5433,7 +5465,7 @@
         <v>17</v>
       </c>
       <c r="F166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G166" t="s">
         <v>18</v>
@@ -5462,7 +5494,7 @@
         <v>17</v>
       </c>
       <c r="F167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G167" t="s">
         <v>18</v>
@@ -5491,7 +5523,7 @@
         <v>17</v>
       </c>
       <c r="F168">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G168" t="s">
         <v>18</v>
@@ -5520,7 +5552,7 @@
         <v>17</v>
       </c>
       <c r="F169">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G169" t="s">
         <v>18</v>
@@ -5532,7 +5564,7 @@
         <v>21</v>
       </c>
       <c r="J169" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.25">
@@ -5549,7 +5581,7 @@
         <v>17</v>
       </c>
       <c r="F170">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G170" t="s">
         <v>18</v>
@@ -5578,7 +5610,7 @@
         <v>17</v>
       </c>
       <c r="F171">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G171" t="s">
         <v>18</v>
@@ -5607,7 +5639,7 @@
         <v>17</v>
       </c>
       <c r="F172">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G172" t="s">
         <v>18</v>
@@ -5619,7 +5651,7 @@
         <v>21</v>
       </c>
       <c r="J172" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.25">
@@ -5636,7 +5668,7 @@
         <v>17</v>
       </c>
       <c r="F173">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G173" t="s">
         <v>18</v>
@@ -5645,10 +5677,10 @@
         <v>17</v>
       </c>
       <c r="I173" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J173" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="174" spans="2:10" x14ac:dyDescent="0.25">
@@ -5665,7 +5697,7 @@
         <v>17</v>
       </c>
       <c r="F174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G174" t="s">
         <v>18</v>
@@ -5694,7 +5726,7 @@
         <v>17</v>
       </c>
       <c r="F175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G175" t="s">
         <v>18</v>
@@ -5723,7 +5755,7 @@
         <v>17</v>
       </c>
       <c r="F176">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G176" t="s">
         <v>18</v>
@@ -5752,7 +5784,7 @@
         <v>17</v>
       </c>
       <c r="F177">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G177" t="s">
         <v>18</v>
@@ -5781,7 +5813,7 @@
         <v>17</v>
       </c>
       <c r="F178">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G178" t="s">
         <v>18</v>
@@ -5793,7 +5825,7 @@
         <v>24</v>
       </c>
       <c r="J178" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.25">
@@ -5810,7 +5842,7 @@
         <v>17</v>
       </c>
       <c r="F179">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G179" t="s">
         <v>18</v>
@@ -5839,7 +5871,7 @@
         <v>17</v>
       </c>
       <c r="F180">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G180" t="s">
         <v>18</v>
@@ -5868,7 +5900,7 @@
         <v>17</v>
       </c>
       <c r="F181">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G181" t="s">
         <v>18</v>
@@ -5880,7 +5912,7 @@
         <v>24</v>
       </c>
       <c r="J181" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.25">
@@ -5897,7 +5929,7 @@
         <v>17</v>
       </c>
       <c r="F182">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G182" t="s">
         <v>18</v>
@@ -5906,10 +5938,10 @@
         <v>17</v>
       </c>
       <c r="I182" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J182" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.25">
@@ -5926,7 +5958,7 @@
         <v>17</v>
       </c>
       <c r="F183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G183" t="s">
         <v>18</v>
@@ -5955,7 +5987,7 @@
         <v>17</v>
       </c>
       <c r="F184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G184" t="s">
         <v>18</v>
@@ -5984,7 +6016,7 @@
         <v>17</v>
       </c>
       <c r="F185">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G185" t="s">
         <v>18</v>
@@ -6013,7 +6045,7 @@
         <v>17</v>
       </c>
       <c r="F186">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G186" t="s">
         <v>18</v>
@@ -6042,7 +6074,7 @@
         <v>17</v>
       </c>
       <c r="F187">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G187" t="s">
         <v>18</v>
@@ -6054,7 +6086,7 @@
         <v>25</v>
       </c>
       <c r="J187" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.25">
@@ -6071,7 +6103,7 @@
         <v>17</v>
       </c>
       <c r="F188">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G188" t="s">
         <v>18</v>
@@ -6100,7 +6132,7 @@
         <v>17</v>
       </c>
       <c r="F189">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G189" t="s">
         <v>18</v>
@@ -6129,7 +6161,7 @@
         <v>17</v>
       </c>
       <c r="F190">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G190" t="s">
         <v>18</v>
@@ -6141,7 +6173,7 @@
         <v>25</v>
       </c>
       <c r="J190" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.25">
@@ -6149,16 +6181,16 @@
         <v>14</v>
       </c>
       <c r="C191" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D191" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E191" t="s">
         <v>17</v>
       </c>
       <c r="F191">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G191" t="s">
         <v>18</v>
@@ -6167,10 +6199,10 @@
         <v>17</v>
       </c>
       <c r="I191" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J191" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.25">
@@ -6187,7 +6219,7 @@
         <v>17</v>
       </c>
       <c r="F192">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G192" t="s">
         <v>18</v>
@@ -6216,7 +6248,7 @@
         <v>17</v>
       </c>
       <c r="F193">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G193" t="s">
         <v>18</v>
@@ -6245,7 +6277,7 @@
         <v>17</v>
       </c>
       <c r="F194">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G194" t="s">
         <v>18</v>
@@ -6274,7 +6306,7 @@
         <v>17</v>
       </c>
       <c r="F195">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G195" t="s">
         <v>18</v>
@@ -6283,10 +6315,10 @@
         <v>17</v>
       </c>
       <c r="I195" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J195" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.25">
@@ -6303,7 +6335,7 @@
         <v>17</v>
       </c>
       <c r="F196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G196" t="s">
         <v>18</v>
@@ -6332,7 +6364,7 @@
         <v>17</v>
       </c>
       <c r="F197">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G197" t="s">
         <v>18</v>
@@ -6361,7 +6393,7 @@
         <v>17</v>
       </c>
       <c r="F198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G198" t="s">
         <v>18</v>
@@ -6373,7 +6405,7 @@
         <v>21</v>
       </c>
       <c r="J198" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.25">
@@ -6390,7 +6422,7 @@
         <v>17</v>
       </c>
       <c r="F199">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G199" t="s">
         <v>18</v>
@@ -6419,7 +6451,7 @@
         <v>17</v>
       </c>
       <c r="F200">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G200" t="s">
         <v>18</v>
@@ -6431,7 +6463,7 @@
         <v>21</v>
       </c>
       <c r="J200" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.25">
@@ -6448,7 +6480,7 @@
         <v>17</v>
       </c>
       <c r="F201">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G201" t="s">
         <v>18</v>
@@ -6477,7 +6509,7 @@
         <v>17</v>
       </c>
       <c r="F202">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G202" t="s">
         <v>18</v>
@@ -6506,7 +6538,7 @@
         <v>17</v>
       </c>
       <c r="F203">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G203" t="s">
         <v>18</v>
@@ -6515,10 +6547,10 @@
         <v>17</v>
       </c>
       <c r="I203" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J203" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="2:10" x14ac:dyDescent="0.25">
@@ -6535,7 +6567,7 @@
         <v>17</v>
       </c>
       <c r="F204">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G204" t="s">
         <v>18</v>
@@ -6564,7 +6596,7 @@
         <v>17</v>
       </c>
       <c r="F205">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G205" t="s">
         <v>18</v>
@@ -6593,7 +6625,7 @@
         <v>17</v>
       </c>
       <c r="F206">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G206" t="s">
         <v>18</v>
@@ -6605,7 +6637,7 @@
         <v>24</v>
       </c>
       <c r="J206" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.25">
@@ -6622,7 +6654,7 @@
         <v>17</v>
       </c>
       <c r="F207">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G207" t="s">
         <v>18</v>
@@ -6651,7 +6683,7 @@
         <v>17</v>
       </c>
       <c r="F208">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G208" t="s">
         <v>18</v>
@@ -6663,7 +6695,7 @@
         <v>24</v>
       </c>
       <c r="J208" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.25">
@@ -6680,7 +6712,7 @@
         <v>17</v>
       </c>
       <c r="F209">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G209" t="s">
         <v>18</v>
@@ -6709,7 +6741,7 @@
         <v>17</v>
       </c>
       <c r="F210">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G210" t="s">
         <v>18</v>
@@ -6738,7 +6770,7 @@
         <v>17</v>
       </c>
       <c r="F211">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G211" t="s">
         <v>18</v>
@@ -6747,10 +6779,10 @@
         <v>17</v>
       </c>
       <c r="I211" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J211" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.25">
@@ -6767,7 +6799,7 @@
         <v>17</v>
       </c>
       <c r="F212">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G212" t="s">
         <v>18</v>
@@ -6796,7 +6828,7 @@
         <v>17</v>
       </c>
       <c r="F213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G213" t="s">
         <v>18</v>
@@ -6825,7 +6857,7 @@
         <v>17</v>
       </c>
       <c r="F214">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G214" t="s">
         <v>18</v>
@@ -6837,7 +6869,7 @@
         <v>25</v>
       </c>
       <c r="J214" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.25">
@@ -6854,7 +6886,7 @@
         <v>17</v>
       </c>
       <c r="F215">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G215" t="s">
         <v>18</v>
@@ -6883,7 +6915,7 @@
         <v>17</v>
       </c>
       <c r="F216">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G216" t="s">
         <v>18</v>
@@ -6895,7 +6927,7 @@
         <v>25</v>
       </c>
       <c r="J216" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="217" spans="2:10" x14ac:dyDescent="0.25">
@@ -6912,7 +6944,7 @@
         <v>17</v>
       </c>
       <c r="F217">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G217" t="s">
         <v>18</v>
@@ -6941,7 +6973,7 @@
         <v>17</v>
       </c>
       <c r="F218">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G218" t="s">
         <v>18</v>
@@ -6964,13 +6996,13 @@
         <v>32</v>
       </c>
       <c r="D219" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E219" t="s">
         <v>17</v>
       </c>
       <c r="F219">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G219" t="s">
         <v>18</v>
@@ -6979,10 +7011,10 @@
         <v>17</v>
       </c>
       <c r="I219" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J219" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.25">
@@ -6999,7 +7031,7 @@
         <v>17</v>
       </c>
       <c r="F220">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G220" t="s">
         <v>18</v>
@@ -7028,7 +7060,7 @@
         <v>17</v>
       </c>
       <c r="F221">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G221" t="s">
         <v>18</v>
@@ -7057,7 +7089,7 @@
         <v>17</v>
       </c>
       <c r="F222">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G222" t="s">
         <v>18</v>
@@ -7086,7 +7118,7 @@
         <v>17</v>
       </c>
       <c r="F223">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G223" t="s">
         <v>18</v>
@@ -7095,10 +7127,10 @@
         <v>17</v>
       </c>
       <c r="I223" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J223" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="224" spans="2:10" x14ac:dyDescent="0.25">
@@ -7115,7 +7147,7 @@
         <v>17</v>
       </c>
       <c r="F224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G224" t="s">
         <v>18</v>
@@ -7144,7 +7176,7 @@
         <v>17</v>
       </c>
       <c r="F225">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G225" t="s">
         <v>18</v>
@@ -7173,7 +7205,7 @@
         <v>17</v>
       </c>
       <c r="F226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G226" t="s">
         <v>18</v>
@@ -7202,7 +7234,7 @@
         <v>17</v>
       </c>
       <c r="F227">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G227" t="s">
         <v>18</v>
@@ -7231,7 +7263,7 @@
         <v>17</v>
       </c>
       <c r="F228">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G228" t="s">
         <v>18</v>
@@ -7243,7 +7275,7 @@
         <v>21</v>
       </c>
       <c r="J228" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="229" spans="2:10" x14ac:dyDescent="0.25">
@@ -7260,7 +7292,7 @@
         <v>17</v>
       </c>
       <c r="F229">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G229" t="s">
         <v>18</v>
@@ -7289,7 +7321,7 @@
         <v>17</v>
       </c>
       <c r="F230">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G230" t="s">
         <v>18</v>
@@ -7318,7 +7350,7 @@
         <v>17</v>
       </c>
       <c r="F231">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G231" t="s">
         <v>18</v>
@@ -7327,10 +7359,10 @@
         <v>17</v>
       </c>
       <c r="I231" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J231" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="2:10" x14ac:dyDescent="0.25">
@@ -7347,7 +7379,7 @@
         <v>17</v>
       </c>
       <c r="F232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G232" t="s">
         <v>18</v>
@@ -7376,7 +7408,7 @@
         <v>17</v>
       </c>
       <c r="F233">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G233" t="s">
         <v>18</v>
@@ -7405,7 +7437,7 @@
         <v>17</v>
       </c>
       <c r="F234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G234" t="s">
         <v>18</v>
@@ -7434,7 +7466,7 @@
         <v>17</v>
       </c>
       <c r="F235">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G235" t="s">
         <v>18</v>
@@ -7463,7 +7495,7 @@
         <v>17</v>
       </c>
       <c r="F236">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G236" t="s">
         <v>18</v>
@@ -7475,7 +7507,7 @@
         <v>24</v>
       </c>
       <c r="J236" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="237" spans="2:10" x14ac:dyDescent="0.25">
@@ -7492,7 +7524,7 @@
         <v>17</v>
       </c>
       <c r="F237">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G237" t="s">
         <v>18</v>
@@ -7521,7 +7553,7 @@
         <v>17</v>
       </c>
       <c r="F238">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G238" t="s">
         <v>18</v>
@@ -7550,7 +7582,7 @@
         <v>17</v>
       </c>
       <c r="F239">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G239" t="s">
         <v>18</v>
@@ -7559,10 +7591,10 @@
         <v>17</v>
       </c>
       <c r="I239" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J239" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="2:10" x14ac:dyDescent="0.25">
@@ -7579,7 +7611,7 @@
         <v>17</v>
       </c>
       <c r="F240">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G240" t="s">
         <v>18</v>
@@ -7608,7 +7640,7 @@
         <v>17</v>
       </c>
       <c r="F241">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G241" t="s">
         <v>18</v>
@@ -7637,7 +7669,7 @@
         <v>17</v>
       </c>
       <c r="F242">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G242" t="s">
         <v>18</v>
@@ -7666,7 +7698,7 @@
         <v>17</v>
       </c>
       <c r="F243">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G243" t="s">
         <v>18</v>
@@ -7695,7 +7727,7 @@
         <v>17</v>
       </c>
       <c r="F244">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G244" t="s">
         <v>18</v>
@@ -7707,7 +7739,7 @@
         <v>25</v>
       </c>
       <c r="J244" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="245" spans="2:10" x14ac:dyDescent="0.25">
@@ -7724,7 +7756,7 @@
         <v>17</v>
       </c>
       <c r="F245">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G245" t="s">
         <v>18</v>
@@ -7753,7 +7785,7 @@
         <v>17</v>
       </c>
       <c r="F246">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G246" t="s">
         <v>18</v>
@@ -7776,13 +7808,13 @@
         <v>32</v>
       </c>
       <c r="D247" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E247" t="s">
         <v>17</v>
       </c>
       <c r="F247">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G247" t="s">
         <v>18</v>
@@ -7791,10 +7823,10 @@
         <v>17</v>
       </c>
       <c r="I247" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J247" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="248" spans="2:10" x14ac:dyDescent="0.25">
@@ -7811,7 +7843,7 @@
         <v>17</v>
       </c>
       <c r="F248">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G248" t="s">
         <v>18</v>
@@ -7840,7 +7872,7 @@
         <v>17</v>
       </c>
       <c r="F249">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G249" t="s">
         <v>18</v>
@@ -7869,7 +7901,7 @@
         <v>17</v>
       </c>
       <c r="F250">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G250" t="s">
         <v>18</v>
@@ -7898,7 +7930,7 @@
         <v>17</v>
       </c>
       <c r="F251">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G251" t="s">
         <v>18</v>
@@ -7907,10 +7939,10 @@
         <v>17</v>
       </c>
       <c r="I251" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J251" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="2:10" x14ac:dyDescent="0.25">
@@ -7927,7 +7959,7 @@
         <v>17</v>
       </c>
       <c r="F252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G252" t="s">
         <v>18</v>
@@ -7956,7 +7988,7 @@
         <v>17</v>
       </c>
       <c r="F253">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G253" t="s">
         <v>18</v>
@@ -7985,7 +8017,7 @@
         <v>17</v>
       </c>
       <c r="F254">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G254" t="s">
         <v>18</v>
@@ -8014,7 +8046,7 @@
         <v>17</v>
       </c>
       <c r="F255">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G255" t="s">
         <v>18</v>
@@ -8043,7 +8075,7 @@
         <v>17</v>
       </c>
       <c r="F256">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G256" t="s">
         <v>18</v>
@@ -8055,7 +8087,7 @@
         <v>21</v>
       </c>
       <c r="J256" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="257" spans="2:10" x14ac:dyDescent="0.25">
@@ -8072,7 +8104,7 @@
         <v>17</v>
       </c>
       <c r="F257">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G257" t="s">
         <v>18</v>
@@ -8101,7 +8133,7 @@
         <v>17</v>
       </c>
       <c r="F258">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G258" t="s">
         <v>18</v>
@@ -8130,7 +8162,7 @@
         <v>17</v>
       </c>
       <c r="F259">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G259" t="s">
         <v>18</v>
@@ -8139,10 +8171,10 @@
         <v>17</v>
       </c>
       <c r="I259" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J259" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="2:10" x14ac:dyDescent="0.25">
@@ -8159,7 +8191,7 @@
         <v>17</v>
       </c>
       <c r="F260">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G260" t="s">
         <v>18</v>
@@ -8188,7 +8220,7 @@
         <v>17</v>
       </c>
       <c r="F261">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G261" t="s">
         <v>18</v>
@@ -8217,7 +8249,7 @@
         <v>17</v>
       </c>
       <c r="F262">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G262" t="s">
         <v>18</v>
@@ -8246,7 +8278,7 @@
         <v>17</v>
       </c>
       <c r="F263">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G263" t="s">
         <v>18</v>
@@ -8275,7 +8307,7 @@
         <v>17</v>
       </c>
       <c r="F264">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G264" t="s">
         <v>18</v>
@@ -8287,7 +8319,7 @@
         <v>24</v>
       </c>
       <c r="J264" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="265" spans="2:10" x14ac:dyDescent="0.25">
@@ -8304,7 +8336,7 @@
         <v>17</v>
       </c>
       <c r="F265">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G265" t="s">
         <v>18</v>
@@ -8333,7 +8365,7 @@
         <v>17</v>
       </c>
       <c r="F266">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G266" t="s">
         <v>18</v>
@@ -8362,7 +8394,7 @@
         <v>17</v>
       </c>
       <c r="F267">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G267" t="s">
         <v>18</v>
@@ -8371,10 +8403,10 @@
         <v>17</v>
       </c>
       <c r="I267" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J267" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268" spans="2:10" x14ac:dyDescent="0.25">
@@ -8391,7 +8423,7 @@
         <v>17</v>
       </c>
       <c r="F268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G268" t="s">
         <v>18</v>
@@ -8420,7 +8452,7 @@
         <v>17</v>
       </c>
       <c r="F269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G269" t="s">
         <v>18</v>
@@ -8449,7 +8481,7 @@
         <v>17</v>
       </c>
       <c r="F270">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G270" t="s">
         <v>18</v>
@@ -8478,7 +8510,7 @@
         <v>17</v>
       </c>
       <c r="F271">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G271" t="s">
         <v>18</v>
@@ -8507,7 +8539,7 @@
         <v>17</v>
       </c>
       <c r="F272">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G272" t="s">
         <v>18</v>
@@ -8519,7 +8551,7 @@
         <v>25</v>
       </c>
       <c r="J272" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="273" spans="2:10" x14ac:dyDescent="0.25">
@@ -8536,7 +8568,7 @@
         <v>17</v>
       </c>
       <c r="F273">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G273" t="s">
         <v>18</v>
@@ -8565,7 +8597,7 @@
         <v>17</v>
       </c>
       <c r="F274">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G274" t="s">
         <v>18</v>
@@ -8585,16 +8617,16 @@
         <v>14</v>
       </c>
       <c r="C275" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D275" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E275" t="s">
         <v>17</v>
       </c>
       <c r="F275">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G275" t="s">
         <v>18</v>
@@ -8603,10 +8635,10 @@
         <v>17</v>
       </c>
       <c r="I275" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J275" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="276" spans="2:10" x14ac:dyDescent="0.25">
@@ -8623,7 +8655,7 @@
         <v>17</v>
       </c>
       <c r="F276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G276" t="s">
         <v>18</v>
@@ -8652,7 +8684,7 @@
         <v>17</v>
       </c>
       <c r="F277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G277" t="s">
         <v>18</v>
@@ -8681,7 +8713,7 @@
         <v>17</v>
       </c>
       <c r="F278">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G278" t="s">
         <v>18</v>
@@ -8710,7 +8742,7 @@
         <v>17</v>
       </c>
       <c r="F279">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G279" t="s">
         <v>18</v>
@@ -8739,7 +8771,7 @@
         <v>17</v>
       </c>
       <c r="F280">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G280" t="s">
         <v>18</v>
@@ -8748,10 +8780,10 @@
         <v>17</v>
       </c>
       <c r="I280" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J280" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="281" spans="2:10" x14ac:dyDescent="0.25">
@@ -8768,7 +8800,7 @@
         <v>17</v>
       </c>
       <c r="F281">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G281" t="s">
         <v>18</v>
@@ -8797,7 +8829,7 @@
         <v>17</v>
       </c>
       <c r="F282">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G282" t="s">
         <v>18</v>
@@ -8826,7 +8858,7 @@
         <v>17</v>
       </c>
       <c r="F283">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G283" t="s">
         <v>18</v>
@@ -8855,7 +8887,7 @@
         <v>17</v>
       </c>
       <c r="F284">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G284" t="s">
         <v>18</v>
@@ -8884,7 +8916,7 @@
         <v>17</v>
       </c>
       <c r="F285">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G285" t="s">
         <v>18</v>
@@ -8896,7 +8928,7 @@
         <v>21</v>
       </c>
       <c r="J285" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="286" spans="2:10" x14ac:dyDescent="0.25">
@@ -8913,7 +8945,7 @@
         <v>17</v>
       </c>
       <c r="F286">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G286" t="s">
         <v>18</v>
@@ -8922,10 +8954,10 @@
         <v>17</v>
       </c>
       <c r="I286" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J286" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="287" spans="2:10" x14ac:dyDescent="0.25">
@@ -8942,7 +8974,7 @@
         <v>17</v>
       </c>
       <c r="F287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G287" t="s">
         <v>18</v>
@@ -8971,7 +9003,7 @@
         <v>17</v>
       </c>
       <c r="F288">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G288" t="s">
         <v>18</v>
@@ -9000,7 +9032,7 @@
         <v>17</v>
       </c>
       <c r="F289">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G289" t="s">
         <v>18</v>
@@ -9029,7 +9061,7 @@
         <v>17</v>
       </c>
       <c r="F290">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G290" t="s">
         <v>18</v>
@@ -9058,7 +9090,7 @@
         <v>17</v>
       </c>
       <c r="F291">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G291" t="s">
         <v>18</v>
@@ -9070,7 +9102,7 @@
         <v>24</v>
       </c>
       <c r="J291" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="292" spans="2:10" x14ac:dyDescent="0.25">
@@ -9087,7 +9119,7 @@
         <v>17</v>
       </c>
       <c r="F292">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G292" t="s">
         <v>18</v>
@@ -9096,10 +9128,10 @@
         <v>17</v>
       </c>
       <c r="I292" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J292" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="293" spans="2:10" x14ac:dyDescent="0.25">
@@ -9116,7 +9148,7 @@
         <v>17</v>
       </c>
       <c r="F293">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G293" t="s">
         <v>18</v>
@@ -9145,7 +9177,7 @@
         <v>17</v>
       </c>
       <c r="F294">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G294" t="s">
         <v>18</v>
@@ -9174,7 +9206,7 @@
         <v>17</v>
       </c>
       <c r="F295">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G295" t="s">
         <v>18</v>
@@ -9203,7 +9235,7 @@
         <v>17</v>
       </c>
       <c r="F296">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G296" t="s">
         <v>18</v>
@@ -9232,7 +9264,7 @@
         <v>17</v>
       </c>
       <c r="F297">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G297" t="s">
         <v>18</v>
@@ -9244,7 +9276,7 @@
         <v>25</v>
       </c>
       <c r="J297" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="298" spans="2:10" x14ac:dyDescent="0.25">
@@ -9255,13 +9287,13 @@
         <v>33</v>
       </c>
       <c r="D298" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E298" t="s">
         <v>17</v>
       </c>
       <c r="F298">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G298" t="s">
         <v>18</v>
@@ -9270,10 +9302,10 @@
         <v>17</v>
       </c>
       <c r="I298" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J298" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="299" spans="2:10" x14ac:dyDescent="0.25">
@@ -9290,7 +9322,7 @@
         <v>17</v>
       </c>
       <c r="F299">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G299" t="s">
         <v>18</v>
@@ -9319,7 +9351,7 @@
         <v>17</v>
       </c>
       <c r="F300">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G300" t="s">
         <v>18</v>
@@ -9348,7 +9380,7 @@
         <v>17</v>
       </c>
       <c r="F301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G301" t="s">
         <v>18</v>
@@ -9377,7 +9409,7 @@
         <v>17</v>
       </c>
       <c r="F302">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G302" t="s">
         <v>18</v>
@@ -9406,7 +9438,7 @@
         <v>17</v>
       </c>
       <c r="F303">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G303" t="s">
         <v>18</v>
@@ -9415,10 +9447,10 @@
         <v>17</v>
       </c>
       <c r="I303" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J303" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="304" spans="2:10" x14ac:dyDescent="0.25">
@@ -9435,7 +9467,7 @@
         <v>17</v>
       </c>
       <c r="F304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G304" t="s">
         <v>18</v>
@@ -9464,7 +9496,7 @@
         <v>17</v>
       </c>
       <c r="F305">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G305" t="s">
         <v>18</v>
@@ -9493,7 +9525,7 @@
         <v>17</v>
       </c>
       <c r="F306">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G306" t="s">
         <v>18</v>
@@ -9522,7 +9554,7 @@
         <v>17</v>
       </c>
       <c r="F307">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G307" t="s">
         <v>18</v>
@@ -9551,7 +9583,7 @@
         <v>17</v>
       </c>
       <c r="F308">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G308" t="s">
         <v>18</v>
@@ -9563,7 +9595,7 @@
         <v>21</v>
       </c>
       <c r="J308" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="309" spans="2:10" x14ac:dyDescent="0.25">
@@ -9580,7 +9612,7 @@
         <v>17</v>
       </c>
       <c r="F309">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G309" t="s">
         <v>18</v>
@@ -9589,10 +9621,10 @@
         <v>17</v>
       </c>
       <c r="I309" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J309" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="310" spans="2:10" x14ac:dyDescent="0.25">
@@ -9609,7 +9641,7 @@
         <v>17</v>
       </c>
       <c r="F310">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G310" t="s">
         <v>18</v>
@@ -9638,7 +9670,7 @@
         <v>17</v>
       </c>
       <c r="F311">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G311" t="s">
         <v>18</v>
@@ -9667,7 +9699,7 @@
         <v>17</v>
       </c>
       <c r="F312">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G312" t="s">
         <v>18</v>
@@ -9696,7 +9728,7 @@
         <v>17</v>
       </c>
       <c r="F313">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G313" t="s">
         <v>18</v>
@@ -9725,7 +9757,7 @@
         <v>17</v>
       </c>
       <c r="F314">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G314" t="s">
         <v>18</v>
@@ -9737,7 +9769,7 @@
         <v>24</v>
       </c>
       <c r="J314" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="315" spans="2:10" x14ac:dyDescent="0.25">
@@ -9754,7 +9786,7 @@
         <v>17</v>
       </c>
       <c r="F315">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G315" t="s">
         <v>18</v>
@@ -9763,10 +9795,10 @@
         <v>17</v>
       </c>
       <c r="I315" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J315" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="316" spans="2:10" x14ac:dyDescent="0.25">
@@ -9783,7 +9815,7 @@
         <v>17</v>
       </c>
       <c r="F316">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G316" t="s">
         <v>18</v>
@@ -9812,7 +9844,7 @@
         <v>17</v>
       </c>
       <c r="F317">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G317" t="s">
         <v>18</v>
@@ -9841,7 +9873,7 @@
         <v>17</v>
       </c>
       <c r="F318">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G318" t="s">
         <v>18</v>
@@ -9870,7 +9902,7 @@
         <v>17</v>
       </c>
       <c r="F319">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G319" t="s">
         <v>18</v>
@@ -9899,7 +9931,7 @@
         <v>17</v>
       </c>
       <c r="F320">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G320" t="s">
         <v>18</v>
@@ -9911,7 +9943,7 @@
         <v>25</v>
       </c>
       <c r="J320" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="321" spans="2:10" x14ac:dyDescent="0.25">
@@ -9922,13 +9954,13 @@
         <v>33</v>
       </c>
       <c r="D321" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E321" t="s">
         <v>17</v>
       </c>
       <c r="F321">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G321" t="s">
         <v>18</v>
@@ -9937,10 +9969,10 @@
         <v>17</v>
       </c>
       <c r="I321" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J321" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="322" spans="2:10" x14ac:dyDescent="0.25">
@@ -9957,7 +9989,7 @@
         <v>17</v>
       </c>
       <c r="F322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G322" t="s">
         <v>18</v>
@@ -9986,7 +10018,7 @@
         <v>17</v>
       </c>
       <c r="F323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G323" t="s">
         <v>18</v>
@@ -10015,7 +10047,7 @@
         <v>17</v>
       </c>
       <c r="F324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G324" t="s">
         <v>18</v>
@@ -10044,7 +10076,7 @@
         <v>17</v>
       </c>
       <c r="F325">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G325" t="s">
         <v>18</v>
@@ -10073,7 +10105,7 @@
         <v>17</v>
       </c>
       <c r="F326">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G326" t="s">
         <v>18</v>
@@ -10082,10 +10114,10 @@
         <v>17</v>
       </c>
       <c r="I326" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J326" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="327" spans="2:10" x14ac:dyDescent="0.25">
@@ -10102,7 +10134,7 @@
         <v>17</v>
       </c>
       <c r="F327">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G327" t="s">
         <v>18</v>
@@ -10131,7 +10163,7 @@
         <v>17</v>
       </c>
       <c r="F328">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G328" t="s">
         <v>18</v>
@@ -10160,7 +10192,7 @@
         <v>17</v>
       </c>
       <c r="F329">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G329" t="s">
         <v>18</v>
@@ -10189,7 +10221,7 @@
         <v>17</v>
       </c>
       <c r="F330">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G330" t="s">
         <v>18</v>
@@ -10218,7 +10250,7 @@
         <v>17</v>
       </c>
       <c r="F331">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G331" t="s">
         <v>18</v>
@@ -10230,7 +10262,7 @@
         <v>21</v>
       </c>
       <c r="J331" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="332" spans="2:10" x14ac:dyDescent="0.25">
@@ -10247,7 +10279,7 @@
         <v>17</v>
       </c>
       <c r="F332">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G332" t="s">
         <v>18</v>
@@ -10256,10 +10288,10 @@
         <v>17</v>
       </c>
       <c r="I332" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J332" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="333" spans="2:10" x14ac:dyDescent="0.25">
@@ -10276,7 +10308,7 @@
         <v>17</v>
       </c>
       <c r="F333">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G333" t="s">
         <v>18</v>
@@ -10305,7 +10337,7 @@
         <v>17</v>
       </c>
       <c r="F334">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G334" t="s">
         <v>18</v>
@@ -10334,7 +10366,7 @@
         <v>17</v>
       </c>
       <c r="F335">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G335" t="s">
         <v>18</v>
@@ -10363,7 +10395,7 @@
         <v>17</v>
       </c>
       <c r="F336">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G336" t="s">
         <v>18</v>
@@ -10392,7 +10424,7 @@
         <v>17</v>
       </c>
       <c r="F337">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G337" t="s">
         <v>18</v>
@@ -10404,7 +10436,7 @@
         <v>24</v>
       </c>
       <c r="J337" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="338" spans="2:10" x14ac:dyDescent="0.25">
@@ -10421,7 +10453,7 @@
         <v>17</v>
       </c>
       <c r="F338">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G338" t="s">
         <v>18</v>
@@ -10430,10 +10462,10 @@
         <v>17</v>
       </c>
       <c r="I338" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J338" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="339" spans="2:10" x14ac:dyDescent="0.25">
@@ -10450,7 +10482,7 @@
         <v>17</v>
       </c>
       <c r="F339">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G339" t="s">
         <v>18</v>
@@ -10479,7 +10511,7 @@
         <v>17</v>
       </c>
       <c r="F340">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G340" t="s">
         <v>18</v>
@@ -10508,7 +10540,7 @@
         <v>17</v>
       </c>
       <c r="F341">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G341" t="s">
         <v>18</v>
@@ -10537,7 +10569,7 @@
         <v>17</v>
       </c>
       <c r="F342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G342" t="s">
         <v>18</v>
@@ -10566,7 +10598,7 @@
         <v>17</v>
       </c>
       <c r="F343">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G343" t="s">
         <v>18</v>
@@ -10578,7 +10610,7 @@
         <v>25</v>
       </c>
       <c r="J343" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="344" spans="2:10" x14ac:dyDescent="0.25">
@@ -10586,16 +10618,16 @@
         <v>14</v>
       </c>
       <c r="C344" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D344" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E344" t="s">
         <v>17</v>
       </c>
       <c r="F344">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G344" t="s">
         <v>18</v>
@@ -10604,10 +10636,10 @@
         <v>17</v>
       </c>
       <c r="I344" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J344" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="345" spans="2:10" x14ac:dyDescent="0.25">
@@ -10624,7 +10656,7 @@
         <v>17</v>
       </c>
       <c r="F345">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G345" t="s">
         <v>18</v>
@@ -10653,7 +10685,7 @@
         <v>17</v>
       </c>
       <c r="F346">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G346" t="s">
         <v>18</v>
@@ -10665,7 +10697,7 @@
         <v>19</v>
       </c>
       <c r="J346" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="347" spans="2:10" x14ac:dyDescent="0.25">
@@ -10682,7 +10714,7 @@
         <v>17</v>
       </c>
       <c r="F347">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G347" t="s">
         <v>18</v>
@@ -10711,7 +10743,7 @@
         <v>17</v>
       </c>
       <c r="F348">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G348" t="s">
         <v>18</v>
@@ -10740,7 +10772,7 @@
         <v>17</v>
       </c>
       <c r="F349">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G349" t="s">
         <v>18</v>
@@ -10749,10 +10781,10 @@
         <v>17</v>
       </c>
       <c r="I349" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J349" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="350" spans="2:10" x14ac:dyDescent="0.25">
@@ -10769,7 +10801,7 @@
         <v>17</v>
       </c>
       <c r="F350">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G350" t="s">
         <v>18</v>
@@ -10798,7 +10830,7 @@
         <v>17</v>
       </c>
       <c r="F351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G351" t="s">
         <v>18</v>
@@ -10807,7 +10839,7 @@
         <v>17</v>
       </c>
       <c r="I351" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J351" t="s">
         <v>31</v>
@@ -10827,7 +10859,7 @@
         <v>17</v>
       </c>
       <c r="F352">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G352" t="s">
         <v>18</v>
@@ -10856,7 +10888,7 @@
         <v>17</v>
       </c>
       <c r="F353">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G353" t="s">
         <v>18</v>
@@ -10865,7 +10897,7 @@
         <v>17</v>
       </c>
       <c r="I353" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J353" t="s">
         <v>31</v>
@@ -10885,7 +10917,7 @@
         <v>17</v>
       </c>
       <c r="F354">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G354" t="s">
         <v>18</v>
@@ -10908,13 +10940,13 @@
         <v>35</v>
       </c>
       <c r="D355" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E355" t="s">
         <v>17</v>
       </c>
       <c r="F355">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G355" t="s">
         <v>18</v>
@@ -10923,10 +10955,10 @@
         <v>17</v>
       </c>
       <c r="I355" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J355" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="356" spans="2:10" x14ac:dyDescent="0.25">
@@ -10943,7 +10975,7 @@
         <v>17</v>
       </c>
       <c r="F356">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G356" t="s">
         <v>18</v>
@@ -10972,7 +11004,7 @@
         <v>17</v>
       </c>
       <c r="F357">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G357" t="s">
         <v>18</v>
@@ -11001,7 +11033,7 @@
         <v>17</v>
       </c>
       <c r="F358">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G358" t="s">
         <v>18</v>
@@ -11030,7 +11062,7 @@
         <v>17</v>
       </c>
       <c r="F359">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G359" t="s">
         <v>18</v>
@@ -11059,7 +11091,7 @@
         <v>17</v>
       </c>
       <c r="F360">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G360" t="s">
         <v>18</v>
@@ -11068,10 +11100,10 @@
         <v>17</v>
       </c>
       <c r="I360" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J360" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="361" spans="2:10" x14ac:dyDescent="0.25">
@@ -11088,7 +11120,7 @@
         <v>17</v>
       </c>
       <c r="F361">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G361" t="s">
         <v>18</v>
@@ -11117,7 +11149,7 @@
         <v>17</v>
       </c>
       <c r="F362">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G362" t="s">
         <v>18</v>
@@ -11126,7 +11158,7 @@
         <v>17</v>
       </c>
       <c r="I362" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J362" t="s">
         <v>31</v>
@@ -11146,7 +11178,7 @@
         <v>17</v>
       </c>
       <c r="F363">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G363" t="s">
         <v>18</v>
@@ -11175,7 +11207,7 @@
         <v>17</v>
       </c>
       <c r="F364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G364" t="s">
         <v>18</v>
@@ -11184,7 +11216,7 @@
         <v>17</v>
       </c>
       <c r="I364" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J364" t="s">
         <v>31</v>
@@ -11204,7 +11236,7 @@
         <v>17</v>
       </c>
       <c r="F365">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G365" t="s">
         <v>18</v>
@@ -11227,13 +11259,13 @@
         <v>35</v>
       </c>
       <c r="D366" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E366" t="s">
         <v>17</v>
       </c>
       <c r="F366">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G366" t="s">
         <v>18</v>
@@ -11242,10 +11274,10 @@
         <v>17</v>
       </c>
       <c r="I366" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J366" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="367" spans="2:10" x14ac:dyDescent="0.25">
@@ -11262,7 +11294,7 @@
         <v>17</v>
       </c>
       <c r="F367">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G367" t="s">
         <v>18</v>
@@ -11291,7 +11323,7 @@
         <v>17</v>
       </c>
       <c r="F368">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G368" t="s">
         <v>18</v>
@@ -11320,7 +11352,7 @@
         <v>17</v>
       </c>
       <c r="F369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G369" t="s">
         <v>18</v>
@@ -11349,7 +11381,7 @@
         <v>17</v>
       </c>
       <c r="F370">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G370" t="s">
         <v>18</v>
@@ -11378,7 +11410,7 @@
         <v>17</v>
       </c>
       <c r="F371">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G371" t="s">
         <v>18</v>
@@ -11387,10 +11419,10 @@
         <v>17</v>
       </c>
       <c r="I371" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J371" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="372" spans="2:10" x14ac:dyDescent="0.25">
@@ -11407,7 +11439,7 @@
         <v>17</v>
       </c>
       <c r="F372">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G372" t="s">
         <v>18</v>
@@ -11436,7 +11468,7 @@
         <v>17</v>
       </c>
       <c r="F373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G373" t="s">
         <v>18</v>
@@ -11445,7 +11477,7 @@
         <v>17</v>
       </c>
       <c r="I373" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J373" t="s">
         <v>31</v>
@@ -11465,7 +11497,7 @@
         <v>17</v>
       </c>
       <c r="F374">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G374" t="s">
         <v>18</v>
@@ -11494,7 +11526,7 @@
         <v>17</v>
       </c>
       <c r="F375">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G375" t="s">
         <v>18</v>
@@ -11503,7 +11535,7 @@
         <v>17</v>
       </c>
       <c r="I375" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J375" t="s">
         <v>31</v>
@@ -11523,7 +11555,7 @@
         <v>17</v>
       </c>
       <c r="F376">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G376" t="s">
         <v>18</v>
@@ -11543,28 +11575,28 @@
         <v>14</v>
       </c>
       <c r="C377" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D377" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E377" t="s">
         <v>17</v>
       </c>
       <c r="F377">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G377" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H377" t="s">
         <v>17</v>
       </c>
       <c r="I377" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J377" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="378" spans="2:10" x14ac:dyDescent="0.25">
@@ -11581,7 +11613,7 @@
         <v>17</v>
       </c>
       <c r="F378">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G378" t="s">
         <v>37</v>
@@ -11610,7 +11642,7 @@
         <v>17</v>
       </c>
       <c r="F379">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G379" t="s">
         <v>37</v>
@@ -11619,10 +11651,10 @@
         <v>17</v>
       </c>
       <c r="I379" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J379" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="380" spans="2:10" x14ac:dyDescent="0.25">
@@ -11639,7 +11671,7 @@
         <v>17</v>
       </c>
       <c r="F380">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G380" t="s">
         <v>37</v>
@@ -11668,7 +11700,7 @@
         <v>17</v>
       </c>
       <c r="F381">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G381" t="s">
         <v>37</v>
@@ -11697,7 +11729,7 @@
         <v>17</v>
       </c>
       <c r="F382">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G382" t="s">
         <v>37</v>
@@ -11709,7 +11741,7 @@
         <v>21</v>
       </c>
       <c r="J382" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="383" spans="2:10" x14ac:dyDescent="0.25">
@@ -11726,7 +11758,7 @@
         <v>17</v>
       </c>
       <c r="F383">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G383" t="s">
         <v>37</v>
@@ -11755,7 +11787,7 @@
         <v>17</v>
       </c>
       <c r="F384">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G384" t="s">
         <v>37</v>
@@ -11764,10 +11796,10 @@
         <v>17</v>
       </c>
       <c r="I384" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J384" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="385" spans="2:10" x14ac:dyDescent="0.25">
@@ -11784,7 +11816,7 @@
         <v>17</v>
       </c>
       <c r="F385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G385" t="s">
         <v>37</v>
@@ -11813,7 +11845,7 @@
         <v>17</v>
       </c>
       <c r="F386">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G386" t="s">
         <v>37</v>
@@ -11842,7 +11874,7 @@
         <v>17</v>
       </c>
       <c r="F387">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G387" t="s">
         <v>37</v>
@@ -11854,7 +11886,7 @@
         <v>24</v>
       </c>
       <c r="J387" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="388" spans="2:10" x14ac:dyDescent="0.25">
@@ -11871,7 +11903,7 @@
         <v>17</v>
       </c>
       <c r="F388">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G388" t="s">
         <v>37</v>
@@ -11900,7 +11932,7 @@
         <v>17</v>
       </c>
       <c r="F389">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G389" t="s">
         <v>37</v>
@@ -11909,10 +11941,10 @@
         <v>17</v>
       </c>
       <c r="I389" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J389" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="390" spans="2:10" x14ac:dyDescent="0.25">
@@ -11929,7 +11961,7 @@
         <v>17</v>
       </c>
       <c r="F390">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G390" t="s">
         <v>37</v>
@@ -11958,7 +11990,7 @@
         <v>17</v>
       </c>
       <c r="F391">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G391" t="s">
         <v>37</v>
@@ -11987,7 +12019,7 @@
         <v>17</v>
       </c>
       <c r="F392">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G392" t="s">
         <v>37</v>
@@ -11999,7 +12031,7 @@
         <v>25</v>
       </c>
       <c r="J392" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="393" spans="2:10" x14ac:dyDescent="0.25">
@@ -12016,7 +12048,7 @@
         <v>17</v>
       </c>
       <c r="F393">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G393" t="s">
         <v>37</v>
@@ -12039,13 +12071,13 @@
         <v>30</v>
       </c>
       <c r="D394" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E394" t="s">
         <v>17</v>
       </c>
       <c r="F394">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G394" t="s">
         <v>37</v>
@@ -12054,10 +12086,10 @@
         <v>17</v>
       </c>
       <c r="I394" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J394" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="395" spans="2:10" x14ac:dyDescent="0.25">
@@ -12074,7 +12106,7 @@
         <v>17</v>
       </c>
       <c r="F395">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G395" t="s">
         <v>37</v>
@@ -12103,7 +12135,7 @@
         <v>17</v>
       </c>
       <c r="F396">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G396" t="s">
         <v>37</v>
@@ -12112,10 +12144,10 @@
         <v>17</v>
       </c>
       <c r="I396" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J396" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="397" spans="2:10" x14ac:dyDescent="0.25">
@@ -12132,7 +12164,7 @@
         <v>17</v>
       </c>
       <c r="F397">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G397" t="s">
         <v>37</v>
@@ -12161,7 +12193,7 @@
         <v>17</v>
       </c>
       <c r="F398">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G398" t="s">
         <v>37</v>
@@ -12190,7 +12222,7 @@
         <v>17</v>
       </c>
       <c r="F399">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G399" t="s">
         <v>37</v>
@@ -12202,7 +12234,7 @@
         <v>21</v>
       </c>
       <c r="J399" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="400" spans="2:10" x14ac:dyDescent="0.25">
@@ -12219,7 +12251,7 @@
         <v>17</v>
       </c>
       <c r="F400">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G400" t="s">
         <v>37</v>
@@ -12248,7 +12280,7 @@
         <v>17</v>
       </c>
       <c r="F401">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G401" t="s">
         <v>37</v>
@@ -12257,10 +12289,10 @@
         <v>17</v>
       </c>
       <c r="I401" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J401" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="402" spans="2:10" x14ac:dyDescent="0.25">
@@ -12277,7 +12309,7 @@
         <v>17</v>
       </c>
       <c r="F402">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G402" t="s">
         <v>37</v>
@@ -12306,7 +12338,7 @@
         <v>17</v>
       </c>
       <c r="F403">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G403" t="s">
         <v>37</v>
@@ -12335,7 +12367,7 @@
         <v>17</v>
       </c>
       <c r="F404">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G404" t="s">
         <v>37</v>
@@ -12347,7 +12379,7 @@
         <v>24</v>
       </c>
       <c r="J404" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="405" spans="2:10" x14ac:dyDescent="0.25">
@@ -12364,7 +12396,7 @@
         <v>17</v>
       </c>
       <c r="F405">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G405" t="s">
         <v>37</v>
@@ -12393,7 +12425,7 @@
         <v>17</v>
       </c>
       <c r="F406">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G406" t="s">
         <v>37</v>
@@ -12402,10 +12434,10 @@
         <v>17</v>
       </c>
       <c r="I406" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J406" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="407" spans="2:10" x14ac:dyDescent="0.25">
@@ -12422,7 +12454,7 @@
         <v>17</v>
       </c>
       <c r="F407">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G407" t="s">
         <v>37</v>
@@ -12451,7 +12483,7 @@
         <v>17</v>
       </c>
       <c r="F408">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G408" t="s">
         <v>37</v>
@@ -12480,7 +12512,7 @@
         <v>17</v>
       </c>
       <c r="F409">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G409" t="s">
         <v>37</v>
@@ -12492,7 +12524,7 @@
         <v>25</v>
       </c>
       <c r="J409" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="410" spans="2:10" x14ac:dyDescent="0.25">
@@ -12509,7 +12541,7 @@
         <v>17</v>
       </c>
       <c r="F410">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G410" t="s">
         <v>37</v>
@@ -12532,13 +12564,13 @@
         <v>30</v>
       </c>
       <c r="D411" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E411" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F411">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G411" t="s">
         <v>37</v>
@@ -12547,10 +12579,10 @@
         <v>17</v>
       </c>
       <c r="I411" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J411" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="2:10" x14ac:dyDescent="0.25">
@@ -12567,7 +12599,7 @@
         <v>38</v>
       </c>
       <c r="F412">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G412" t="s">
         <v>37</v>
@@ -12596,7 +12628,7 @@
         <v>38</v>
       </c>
       <c r="F413">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G413" t="s">
         <v>37</v>
@@ -12605,10 +12637,10 @@
         <v>17</v>
       </c>
       <c r="I413" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J413" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="414" spans="2:10" x14ac:dyDescent="0.25">
@@ -12625,7 +12657,7 @@
         <v>38</v>
       </c>
       <c r="F414">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G414" t="s">
         <v>37</v>
@@ -12654,7 +12686,7 @@
         <v>38</v>
       </c>
       <c r="F415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G415" t="s">
         <v>37</v>
@@ -12683,7 +12715,7 @@
         <v>38</v>
       </c>
       <c r="F416">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G416" t="s">
         <v>37</v>
@@ -12695,7 +12727,7 @@
         <v>21</v>
       </c>
       <c r="J416" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="417" spans="2:10" x14ac:dyDescent="0.25">
@@ -12712,7 +12744,7 @@
         <v>38</v>
       </c>
       <c r="F417">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G417" t="s">
         <v>37</v>
@@ -12741,7 +12773,7 @@
         <v>38</v>
       </c>
       <c r="F418">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G418" t="s">
         <v>37</v>
@@ -12750,10 +12782,10 @@
         <v>17</v>
       </c>
       <c r="I418" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J418" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="419" spans="2:10" x14ac:dyDescent="0.25">
@@ -12770,7 +12802,7 @@
         <v>38</v>
       </c>
       <c r="F419">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G419" t="s">
         <v>37</v>
@@ -12799,7 +12831,7 @@
         <v>38</v>
       </c>
       <c r="F420">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G420" t="s">
         <v>37</v>
@@ -12828,7 +12860,7 @@
         <v>38</v>
       </c>
       <c r="F421">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G421" t="s">
         <v>37</v>
@@ -12840,7 +12872,7 @@
         <v>24</v>
       </c>
       <c r="J421" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="422" spans="2:10" x14ac:dyDescent="0.25">
@@ -12857,7 +12889,7 @@
         <v>38</v>
       </c>
       <c r="F422">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G422" t="s">
         <v>37</v>
@@ -12886,7 +12918,7 @@
         <v>38</v>
       </c>
       <c r="F423">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G423" t="s">
         <v>37</v>
@@ -12895,10 +12927,10 @@
         <v>17</v>
       </c>
       <c r="I423" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J423" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="424" spans="2:10" x14ac:dyDescent="0.25">
@@ -12915,7 +12947,7 @@
         <v>38</v>
       </c>
       <c r="F424">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G424" t="s">
         <v>37</v>
@@ -12944,7 +12976,7 @@
         <v>38</v>
       </c>
       <c r="F425">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G425" t="s">
         <v>37</v>
@@ -12973,7 +13005,7 @@
         <v>38</v>
       </c>
       <c r="F426">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G426" t="s">
         <v>37</v>
@@ -12985,7 +13017,7 @@
         <v>25</v>
       </c>
       <c r="J426" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="427" spans="2:10" x14ac:dyDescent="0.25">
@@ -13002,7 +13034,7 @@
         <v>38</v>
       </c>
       <c r="F427">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G427" t="s">
         <v>37</v>
@@ -13025,13 +13057,13 @@
         <v>30</v>
       </c>
       <c r="D428" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E428" t="s">
         <v>38</v>
       </c>
       <c r="F428">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G428" t="s">
         <v>37</v>
@@ -13040,10 +13072,10 @@
         <v>17</v>
       </c>
       <c r="I428" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J428" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="429" spans="2:10" x14ac:dyDescent="0.25">
@@ -13060,7 +13092,7 @@
         <v>38</v>
       </c>
       <c r="F429">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G429" t="s">
         <v>37</v>
@@ -13089,7 +13121,7 @@
         <v>38</v>
       </c>
       <c r="F430">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G430" t="s">
         <v>37</v>
@@ -13098,10 +13130,10 @@
         <v>17</v>
       </c>
       <c r="I430" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J430" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="431" spans="2:10" x14ac:dyDescent="0.25">
@@ -13118,7 +13150,7 @@
         <v>38</v>
       </c>
       <c r="F431">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G431" t="s">
         <v>37</v>
@@ -13147,7 +13179,7 @@
         <v>38</v>
       </c>
       <c r="F432">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G432" t="s">
         <v>37</v>
@@ -13176,7 +13208,7 @@
         <v>38</v>
       </c>
       <c r="F433">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G433" t="s">
         <v>37</v>
@@ -13188,7 +13220,7 @@
         <v>21</v>
       </c>
       <c r="J433" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="434" spans="2:10" x14ac:dyDescent="0.25">
@@ -13205,7 +13237,7 @@
         <v>38</v>
       </c>
       <c r="F434">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G434" t="s">
         <v>37</v>
@@ -13234,7 +13266,7 @@
         <v>38</v>
       </c>
       <c r="F435">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G435" t="s">
         <v>37</v>
@@ -13243,10 +13275,10 @@
         <v>17</v>
       </c>
       <c r="I435" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J435" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="436" spans="2:10" x14ac:dyDescent="0.25">
@@ -13263,7 +13295,7 @@
         <v>38</v>
       </c>
       <c r="F436">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G436" t="s">
         <v>37</v>
@@ -13292,7 +13324,7 @@
         <v>38</v>
       </c>
       <c r="F437">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G437" t="s">
         <v>37</v>
@@ -13321,7 +13353,7 @@
         <v>38</v>
       </c>
       <c r="F438">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G438" t="s">
         <v>37</v>
@@ -13333,7 +13365,7 @@
         <v>24</v>
       </c>
       <c r="J438" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="439" spans="2:10" x14ac:dyDescent="0.25">
@@ -13350,7 +13382,7 @@
         <v>38</v>
       </c>
       <c r="F439">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G439" t="s">
         <v>37</v>
@@ -13379,7 +13411,7 @@
         <v>38</v>
       </c>
       <c r="F440">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G440" t="s">
         <v>37</v>
@@ -13388,10 +13420,10 @@
         <v>17</v>
       </c>
       <c r="I440" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J440" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="441" spans="2:10" x14ac:dyDescent="0.25">
@@ -13408,7 +13440,7 @@
         <v>38</v>
       </c>
       <c r="F441">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G441" t="s">
         <v>37</v>
@@ -13437,7 +13469,7 @@
         <v>38</v>
       </c>
       <c r="F442">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G442" t="s">
         <v>37</v>
@@ -13466,7 +13498,7 @@
         <v>38</v>
       </c>
       <c r="F443">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G443" t="s">
         <v>37</v>
@@ -13478,7 +13510,7 @@
         <v>25</v>
       </c>
       <c r="J443" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="444" spans="2:10" x14ac:dyDescent="0.25">
@@ -13495,7 +13527,7 @@
         <v>38</v>
       </c>
       <c r="F444">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G444" t="s">
         <v>37</v>
@@ -13515,16 +13547,16 @@
         <v>14</v>
       </c>
       <c r="C445" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D445" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E445" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F445">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G445" t="s">
         <v>37</v>
@@ -13533,10 +13565,10 @@
         <v>17</v>
       </c>
       <c r="I445" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J445" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="446" spans="2:10" x14ac:dyDescent="0.25">
@@ -13553,7 +13585,7 @@
         <v>17</v>
       </c>
       <c r="F446">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G446" t="s">
         <v>37</v>
@@ -13582,7 +13614,7 @@
         <v>17</v>
       </c>
       <c r="F447">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G447" t="s">
         <v>37</v>
@@ -13591,10 +13623,10 @@
         <v>17</v>
       </c>
       <c r="I447" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J447" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="448" spans="2:10" x14ac:dyDescent="0.25">
@@ -13611,7 +13643,7 @@
         <v>17</v>
       </c>
       <c r="F448">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G448" t="s">
         <v>37</v>
@@ -13640,7 +13672,7 @@
         <v>17</v>
       </c>
       <c r="F449">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G449" t="s">
         <v>37</v>
@@ -13669,7 +13701,7 @@
         <v>17</v>
       </c>
       <c r="F450">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G450" t="s">
         <v>37</v>
@@ -13681,7 +13713,7 @@
         <v>21</v>
       </c>
       <c r="J450" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="451" spans="2:10" x14ac:dyDescent="0.25">
@@ -13698,7 +13730,7 @@
         <v>17</v>
       </c>
       <c r="F451">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G451" t="s">
         <v>37</v>
@@ -13727,7 +13759,7 @@
         <v>17</v>
       </c>
       <c r="F452">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G452" t="s">
         <v>37</v>
@@ -13736,10 +13768,10 @@
         <v>17</v>
       </c>
       <c r="I452" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J452" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="453" spans="2:10" x14ac:dyDescent="0.25">
@@ -13756,7 +13788,7 @@
         <v>17</v>
       </c>
       <c r="F453">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G453" t="s">
         <v>37</v>
@@ -13785,7 +13817,7 @@
         <v>17</v>
       </c>
       <c r="F454">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G454" t="s">
         <v>37</v>
@@ -13814,7 +13846,7 @@
         <v>17</v>
       </c>
       <c r="F455">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G455" t="s">
         <v>37</v>
@@ -13826,7 +13858,7 @@
         <v>24</v>
       </c>
       <c r="J455" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="456" spans="2:10" x14ac:dyDescent="0.25">
@@ -13843,7 +13875,7 @@
         <v>17</v>
       </c>
       <c r="F456">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G456" t="s">
         <v>37</v>
@@ -13872,7 +13904,7 @@
         <v>17</v>
       </c>
       <c r="F457">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G457" t="s">
         <v>37</v>
@@ -13881,10 +13913,10 @@
         <v>17</v>
       </c>
       <c r="I457" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J457" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="458" spans="2:10" x14ac:dyDescent="0.25">
@@ -13901,7 +13933,7 @@
         <v>17</v>
       </c>
       <c r="F458">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G458" t="s">
         <v>37</v>
@@ -13930,7 +13962,7 @@
         <v>17</v>
       </c>
       <c r="F459">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G459" t="s">
         <v>37</v>
@@ -13959,7 +13991,7 @@
         <v>17</v>
       </c>
       <c r="F460">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G460" t="s">
         <v>37</v>
@@ -13971,7 +14003,7 @@
         <v>25</v>
       </c>
       <c r="J460" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="461" spans="2:10" x14ac:dyDescent="0.25">
@@ -13988,7 +14020,7 @@
         <v>17</v>
       </c>
       <c r="F461">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G461" t="s">
         <v>37</v>
@@ -14011,13 +14043,13 @@
         <v>32</v>
       </c>
       <c r="D462" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E462" t="s">
         <v>17</v>
       </c>
       <c r="F462">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G462" t="s">
         <v>37</v>
@@ -14026,10 +14058,10 @@
         <v>17</v>
       </c>
       <c r="I462" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J462" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="463" spans="2:10" x14ac:dyDescent="0.25">
@@ -14046,7 +14078,7 @@
         <v>17</v>
       </c>
       <c r="F463">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G463" t="s">
         <v>37</v>
@@ -14058,7 +14090,7 @@
         <v>19</v>
       </c>
       <c r="J463" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="464" spans="2:10" x14ac:dyDescent="0.25">
@@ -14075,7 +14107,7 @@
         <v>17</v>
       </c>
       <c r="F464">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G464" t="s">
         <v>37</v>
@@ -14084,10 +14116,10 @@
         <v>17</v>
       </c>
       <c r="I464" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J464" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="465" spans="2:10" x14ac:dyDescent="0.25">
@@ -14104,7 +14136,7 @@
         <v>17</v>
       </c>
       <c r="F465">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G465" t="s">
         <v>37</v>
@@ -14133,7 +14165,7 @@
         <v>17</v>
       </c>
       <c r="F466">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G466" t="s">
         <v>37</v>
@@ -14162,7 +14194,7 @@
         <v>17</v>
       </c>
       <c r="F467">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G467" t="s">
         <v>37</v>
@@ -14174,7 +14206,7 @@
         <v>21</v>
       </c>
       <c r="J467" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="468" spans="2:10" x14ac:dyDescent="0.25">
@@ -14191,7 +14223,7 @@
         <v>17</v>
       </c>
       <c r="F468">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G468" t="s">
         <v>37</v>
@@ -14203,7 +14235,7 @@
         <v>21</v>
       </c>
       <c r="J468" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="469" spans="2:10" x14ac:dyDescent="0.25">
@@ -14220,7 +14252,7 @@
         <v>17</v>
       </c>
       <c r="F469">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G469" t="s">
         <v>37</v>
@@ -14229,10 +14261,10 @@
         <v>17</v>
       </c>
       <c r="I469" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J469" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="470" spans="2:10" x14ac:dyDescent="0.25">
@@ -14249,7 +14281,7 @@
         <v>17</v>
       </c>
       <c r="F470">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G470" t="s">
         <v>37</v>
@@ -14278,7 +14310,7 @@
         <v>17</v>
       </c>
       <c r="F471">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G471" t="s">
         <v>37</v>
@@ -14307,7 +14339,7 @@
         <v>17</v>
       </c>
       <c r="F472">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G472" t="s">
         <v>37</v>
@@ -14319,7 +14351,7 @@
         <v>24</v>
       </c>
       <c r="J472" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="473" spans="2:10" x14ac:dyDescent="0.25">
@@ -14336,7 +14368,7 @@
         <v>17</v>
       </c>
       <c r="F473">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G473" t="s">
         <v>37</v>
@@ -14348,7 +14380,7 @@
         <v>24</v>
       </c>
       <c r="J473" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="474" spans="2:10" x14ac:dyDescent="0.25">
@@ -14365,7 +14397,7 @@
         <v>17</v>
       </c>
       <c r="F474">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G474" t="s">
         <v>37</v>
@@ -14374,10 +14406,10 @@
         <v>17</v>
       </c>
       <c r="I474" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J474" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="475" spans="2:10" x14ac:dyDescent="0.25">
@@ -14394,7 +14426,7 @@
         <v>17</v>
       </c>
       <c r="F475">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G475" t="s">
         <v>37</v>
@@ -14423,7 +14455,7 @@
         <v>17</v>
       </c>
       <c r="F476">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G476" t="s">
         <v>37</v>
@@ -14452,7 +14484,7 @@
         <v>17</v>
       </c>
       <c r="F477">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G477" t="s">
         <v>37</v>
@@ -14464,7 +14496,7 @@
         <v>25</v>
       </c>
       <c r="J477" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="478" spans="2:10" x14ac:dyDescent="0.25">
@@ -14481,7 +14513,7 @@
         <v>17</v>
       </c>
       <c r="F478">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G478" t="s">
         <v>37</v>
@@ -14493,7 +14525,7 @@
         <v>25</v>
       </c>
       <c r="J478" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="479" spans="2:10" x14ac:dyDescent="0.25">
@@ -14504,13 +14536,13 @@
         <v>32</v>
       </c>
       <c r="D479" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E479" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F479">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G479" t="s">
         <v>37</v>
@@ -14519,10 +14551,10 @@
         <v>17</v>
       </c>
       <c r="I479" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J479" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="480" spans="2:10" x14ac:dyDescent="0.25">
@@ -14539,7 +14571,7 @@
         <v>38</v>
       </c>
       <c r="F480">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G480" t="s">
         <v>37</v>
@@ -14568,7 +14600,7 @@
         <v>38</v>
       </c>
       <c r="F481">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G481" t="s">
         <v>37</v>
@@ -14577,10 +14609,10 @@
         <v>17</v>
       </c>
       <c r="I481" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J481" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="482" spans="2:10" x14ac:dyDescent="0.25">
@@ -14597,7 +14629,7 @@
         <v>38</v>
       </c>
       <c r="F482">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G482" t="s">
         <v>37</v>
@@ -14626,7 +14658,7 @@
         <v>38</v>
       </c>
       <c r="F483">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G483" t="s">
         <v>37</v>
@@ -14638,7 +14670,7 @@
         <v>21</v>
       </c>
       <c r="J483" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="484" spans="2:10" x14ac:dyDescent="0.25">
@@ -14655,7 +14687,7 @@
         <v>38</v>
       </c>
       <c r="F484">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G484" t="s">
         <v>37</v>
@@ -14667,7 +14699,7 @@
         <v>21</v>
       </c>
       <c r="J484" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="485" spans="2:10" x14ac:dyDescent="0.25">
@@ -14684,7 +14716,7 @@
         <v>38</v>
       </c>
       <c r="F485">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G485" t="s">
         <v>37</v>
@@ -14713,7 +14745,7 @@
         <v>38</v>
       </c>
       <c r="F486">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G486" t="s">
         <v>37</v>
@@ -14722,10 +14754,10 @@
         <v>17</v>
       </c>
       <c r="I486" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J486" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="487" spans="2:10" x14ac:dyDescent="0.25">
@@ -14742,7 +14774,7 @@
         <v>38</v>
       </c>
       <c r="F487">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G487" t="s">
         <v>37</v>
@@ -14771,7 +14803,7 @@
         <v>38</v>
       </c>
       <c r="F488">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G488" t="s">
         <v>37</v>
@@ -14783,7 +14815,7 @@
         <v>24</v>
       </c>
       <c r="J488" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="489" spans="2:10" x14ac:dyDescent="0.25">
@@ -14800,7 +14832,7 @@
         <v>38</v>
       </c>
       <c r="F489">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G489" t="s">
         <v>37</v>
@@ -14812,7 +14844,7 @@
         <v>24</v>
       </c>
       <c r="J489" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="490" spans="2:10" x14ac:dyDescent="0.25">
@@ -14829,7 +14861,7 @@
         <v>38</v>
       </c>
       <c r="F490">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G490" t="s">
         <v>37</v>
@@ -14858,7 +14890,7 @@
         <v>38</v>
       </c>
       <c r="F491">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G491" t="s">
         <v>37</v>
@@ -14867,10 +14899,10 @@
         <v>17</v>
       </c>
       <c r="I491" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J491" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="492" spans="2:10" x14ac:dyDescent="0.25">
@@ -14887,7 +14919,7 @@
         <v>38</v>
       </c>
       <c r="F492">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G492" t="s">
         <v>37</v>
@@ -14916,7 +14948,7 @@
         <v>38</v>
       </c>
       <c r="F493">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G493" t="s">
         <v>37</v>
@@ -14928,7 +14960,7 @@
         <v>25</v>
       </c>
       <c r="J493" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="494" spans="2:10" x14ac:dyDescent="0.25">
@@ -14945,7 +14977,7 @@
         <v>38</v>
       </c>
       <c r="F494">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G494" t="s">
         <v>37</v>
@@ -14957,7 +14989,7 @@
         <v>25</v>
       </c>
       <c r="J494" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="495" spans="2:10" x14ac:dyDescent="0.25">
@@ -14974,7 +15006,7 @@
         <v>38</v>
       </c>
       <c r="F495">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G495" t="s">
         <v>37</v>
@@ -14997,13 +15029,13 @@
         <v>32</v>
       </c>
       <c r="D496" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E496" t="s">
         <v>38</v>
       </c>
       <c r="F496">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G496" t="s">
         <v>37</v>
@@ -15012,10 +15044,10 @@
         <v>17</v>
       </c>
       <c r="I496" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J496" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="497" spans="2:10" x14ac:dyDescent="0.25">
@@ -15032,7 +15064,7 @@
         <v>38</v>
       </c>
       <c r="F497">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G497" t="s">
         <v>37</v>
@@ -15044,7 +15076,7 @@
         <v>19</v>
       </c>
       <c r="J497" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="498" spans="2:10" x14ac:dyDescent="0.25">
@@ -15061,7 +15093,7 @@
         <v>38</v>
       </c>
       <c r="F498">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G498" t="s">
         <v>37</v>
@@ -15070,10 +15102,10 @@
         <v>17</v>
       </c>
       <c r="I498" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J498" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="499" spans="2:10" x14ac:dyDescent="0.25">
@@ -15090,7 +15122,7 @@
         <v>38</v>
       </c>
       <c r="F499">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G499" t="s">
         <v>37</v>
@@ -15119,7 +15151,7 @@
         <v>38</v>
       </c>
       <c r="F500">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G500" t="s">
         <v>37</v>
@@ -15148,7 +15180,7 @@
         <v>38</v>
       </c>
       <c r="F501">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G501" t="s">
         <v>37</v>
@@ -15160,7 +15192,7 @@
         <v>21</v>
       </c>
       <c r="J501" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="502" spans="2:10" x14ac:dyDescent="0.25">
@@ -15177,7 +15209,7 @@
         <v>38</v>
       </c>
       <c r="F502">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G502" t="s">
         <v>37</v>
@@ -15189,7 +15221,7 @@
         <v>21</v>
       </c>
       <c r="J502" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="503" spans="2:10" x14ac:dyDescent="0.25">
@@ -15206,7 +15238,7 @@
         <v>38</v>
       </c>
       <c r="F503">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G503" t="s">
         <v>37</v>
@@ -15215,10 +15247,10 @@
         <v>17</v>
       </c>
       <c r="I503" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J503" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="504" spans="2:10" x14ac:dyDescent="0.25">
@@ -15235,7 +15267,7 @@
         <v>38</v>
       </c>
       <c r="F504">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G504" t="s">
         <v>37</v>
@@ -15264,7 +15296,7 @@
         <v>38</v>
       </c>
       <c r="F505">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G505" t="s">
         <v>37</v>
@@ -15293,7 +15325,7 @@
         <v>38</v>
       </c>
       <c r="F506">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G506" t="s">
         <v>37</v>
@@ -15305,7 +15337,7 @@
         <v>24</v>
       </c>
       <c r="J506" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="507" spans="2:10" x14ac:dyDescent="0.25">
@@ -15322,7 +15354,7 @@
         <v>38</v>
       </c>
       <c r="F507">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G507" t="s">
         <v>37</v>
@@ -15334,7 +15366,7 @@
         <v>24</v>
       </c>
       <c r="J507" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="508" spans="2:10" x14ac:dyDescent="0.25">
@@ -15351,7 +15383,7 @@
         <v>38</v>
       </c>
       <c r="F508">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G508" t="s">
         <v>37</v>
@@ -15360,10 +15392,10 @@
         <v>17</v>
       </c>
       <c r="I508" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J508" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="509" spans="2:10" x14ac:dyDescent="0.25">
@@ -15380,7 +15412,7 @@
         <v>38</v>
       </c>
       <c r="F509">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G509" t="s">
         <v>37</v>
@@ -15409,7 +15441,7 @@
         <v>38</v>
       </c>
       <c r="F510">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G510" t="s">
         <v>37</v>
@@ -15438,7 +15470,7 @@
         <v>38</v>
       </c>
       <c r="F511">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G511" t="s">
         <v>37</v>
@@ -15450,7 +15482,7 @@
         <v>25</v>
       </c>
       <c r="J511" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="512" spans="2:10" x14ac:dyDescent="0.25">
@@ -15467,7 +15499,7 @@
         <v>38</v>
       </c>
       <c r="F512">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G512" t="s">
         <v>37</v>
@@ -15479,7 +15511,7 @@
         <v>25</v>
       </c>
       <c r="J512" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="513" spans="2:10" x14ac:dyDescent="0.25">
@@ -15487,16 +15519,16 @@
         <v>14</v>
       </c>
       <c r="C513" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D513" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E513" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F513">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G513" t="s">
         <v>37</v>
@@ -15505,10 +15537,10 @@
         <v>17</v>
       </c>
       <c r="I513" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J513" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="514" spans="2:10" x14ac:dyDescent="0.25">
@@ -15525,7 +15557,7 @@
         <v>17</v>
       </c>
       <c r="F514">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G514" t="s">
         <v>37</v>
@@ -15554,7 +15586,7 @@
         <v>17</v>
       </c>
       <c r="F515">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G515" t="s">
         <v>37</v>
@@ -15583,7 +15615,7 @@
         <v>17</v>
       </c>
       <c r="F516">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G516" t="s">
         <v>37</v>
@@ -15595,7 +15627,7 @@
         <v>19</v>
       </c>
       <c r="J516" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="517" spans="2:10" x14ac:dyDescent="0.25">
@@ -15612,7 +15644,7 @@
         <v>17</v>
       </c>
       <c r="F517">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G517" t="s">
         <v>37</v>
@@ -15641,7 +15673,7 @@
         <v>17</v>
       </c>
       <c r="F518">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G518" t="s">
         <v>37</v>
@@ -15650,10 +15682,10 @@
         <v>17</v>
       </c>
       <c r="I518" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J518" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="519" spans="2:10" x14ac:dyDescent="0.25">
@@ -15670,7 +15702,7 @@
         <v>17</v>
       </c>
       <c r="F519">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G519" t="s">
         <v>37</v>
@@ -15699,7 +15731,7 @@
         <v>17</v>
       </c>
       <c r="F520">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G520" t="s">
         <v>37</v>
@@ -15728,7 +15760,7 @@
         <v>17</v>
       </c>
       <c r="F521">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G521" t="s">
         <v>37</v>
@@ -15740,7 +15772,7 @@
         <v>21</v>
       </c>
       <c r="J521" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="522" spans="2:10" x14ac:dyDescent="0.25">
@@ -15757,7 +15789,7 @@
         <v>17</v>
       </c>
       <c r="F522">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G522" t="s">
         <v>37</v>
@@ -15786,7 +15818,7 @@
         <v>17</v>
       </c>
       <c r="F523">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G523" t="s">
         <v>37</v>
@@ -15795,10 +15827,10 @@
         <v>17</v>
       </c>
       <c r="I523" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J523" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="524" spans="2:10" x14ac:dyDescent="0.25">
@@ -15815,7 +15847,7 @@
         <v>17</v>
       </c>
       <c r="F524">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G524" t="s">
         <v>37</v>
@@ -15844,7 +15876,7 @@
         <v>17</v>
       </c>
       <c r="F525">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G525" t="s">
         <v>37</v>
@@ -15873,7 +15905,7 @@
         <v>17</v>
       </c>
       <c r="F526">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G526" t="s">
         <v>37</v>
@@ -15885,7 +15917,7 @@
         <v>24</v>
       </c>
       <c r="J526" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="527" spans="2:10" x14ac:dyDescent="0.25">
@@ -15902,7 +15934,7 @@
         <v>17</v>
       </c>
       <c r="F527">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G527" t="s">
         <v>37</v>
@@ -15931,7 +15963,7 @@
         <v>17</v>
       </c>
       <c r="F528">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G528" t="s">
         <v>37</v>
@@ -15940,10 +15972,10 @@
         <v>17</v>
       </c>
       <c r="I528" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J528" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="529" spans="2:10" x14ac:dyDescent="0.25">
@@ -15960,7 +15992,7 @@
         <v>17</v>
       </c>
       <c r="F529">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G529" t="s">
         <v>37</v>
@@ -15989,7 +16021,7 @@
         <v>17</v>
       </c>
       <c r="F530">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G530" t="s">
         <v>37</v>
@@ -16018,7 +16050,7 @@
         <v>17</v>
       </c>
       <c r="F531">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G531" t="s">
         <v>37</v>
@@ -16030,7 +16062,7 @@
         <v>25</v>
       </c>
       <c r="J531" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="532" spans="2:10" x14ac:dyDescent="0.25">
@@ -16047,7 +16079,7 @@
         <v>17</v>
       </c>
       <c r="F532">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G532" t="s">
         <v>37</v>
@@ -16070,13 +16102,13 @@
         <v>33</v>
       </c>
       <c r="D533" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E533" t="s">
         <v>17</v>
       </c>
       <c r="F533">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G533" t="s">
         <v>37</v>
@@ -16085,10 +16117,10 @@
         <v>17</v>
       </c>
       <c r="I533" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J533" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="534" spans="2:10" x14ac:dyDescent="0.25">
@@ -16105,7 +16137,7 @@
         <v>17</v>
       </c>
       <c r="F534">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G534" t="s">
         <v>37</v>
@@ -16134,7 +16166,7 @@
         <v>17</v>
       </c>
       <c r="F535">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G535" t="s">
         <v>37</v>
@@ -16163,7 +16195,7 @@
         <v>17</v>
       </c>
       <c r="F536">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G536" t="s">
         <v>37</v>
@@ -16175,7 +16207,7 @@
         <v>19</v>
       </c>
       <c r="J536" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="537" spans="2:10" x14ac:dyDescent="0.25">
@@ -16192,7 +16224,7 @@
         <v>17</v>
       </c>
       <c r="F537">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G537" t="s">
         <v>37</v>
@@ -16221,7 +16253,7 @@
         <v>17</v>
       </c>
       <c r="F538">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G538" t="s">
         <v>37</v>
@@ -16230,10 +16262,10 @@
         <v>17</v>
       </c>
       <c r="I538" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J538" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="539" spans="2:10" x14ac:dyDescent="0.25">
@@ -16250,7 +16282,7 @@
         <v>17</v>
       </c>
       <c r="F539">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G539" t="s">
         <v>37</v>
@@ -16279,7 +16311,7 @@
         <v>17</v>
       </c>
       <c r="F540">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G540" t="s">
         <v>37</v>
@@ -16308,7 +16340,7 @@
         <v>17</v>
       </c>
       <c r="F541">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G541" t="s">
         <v>37</v>
@@ -16320,7 +16352,7 @@
         <v>21</v>
       </c>
       <c r="J541" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="542" spans="2:10" x14ac:dyDescent="0.25">
@@ -16337,7 +16369,7 @@
         <v>17</v>
       </c>
       <c r="F542">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G542" t="s">
         <v>37</v>
@@ -16366,7 +16398,7 @@
         <v>17</v>
       </c>
       <c r="F543">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G543" t="s">
         <v>37</v>
@@ -16375,10 +16407,10 @@
         <v>17</v>
       </c>
       <c r="I543" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J543" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="544" spans="2:10" x14ac:dyDescent="0.25">
@@ -16395,7 +16427,7 @@
         <v>17</v>
       </c>
       <c r="F544">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G544" t="s">
         <v>37</v>
@@ -16424,7 +16456,7 @@
         <v>17</v>
       </c>
       <c r="F545">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G545" t="s">
         <v>37</v>
@@ -16453,7 +16485,7 @@
         <v>17</v>
       </c>
       <c r="F546">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G546" t="s">
         <v>37</v>
@@ -16465,7 +16497,7 @@
         <v>24</v>
       </c>
       <c r="J546" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="547" spans="2:10" x14ac:dyDescent="0.25">
@@ -16482,7 +16514,7 @@
         <v>17</v>
       </c>
       <c r="F547">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G547" t="s">
         <v>37</v>
@@ -16511,7 +16543,7 @@
         <v>17</v>
       </c>
       <c r="F548">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G548" t="s">
         <v>37</v>
@@ -16520,10 +16552,10 @@
         <v>17</v>
       </c>
       <c r="I548" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J548" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="549" spans="2:10" x14ac:dyDescent="0.25">
@@ -16540,7 +16572,7 @@
         <v>17</v>
       </c>
       <c r="F549">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G549" t="s">
         <v>37</v>
@@ -16569,7 +16601,7 @@
         <v>17</v>
       </c>
       <c r="F550">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G550" t="s">
         <v>37</v>
@@ -16598,7 +16630,7 @@
         <v>17</v>
       </c>
       <c r="F551">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G551" t="s">
         <v>37</v>
@@ -16610,7 +16642,7 @@
         <v>25</v>
       </c>
       <c r="J551" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="552" spans="2:10" x14ac:dyDescent="0.25">
@@ -16627,7 +16659,7 @@
         <v>17</v>
       </c>
       <c r="F552">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G552" t="s">
         <v>37</v>
@@ -16650,13 +16682,13 @@
         <v>33</v>
       </c>
       <c r="D553" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E553" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F553">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G553" t="s">
         <v>37</v>
@@ -16665,10 +16697,10 @@
         <v>17</v>
       </c>
       <c r="I553" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J553" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="554" spans="2:10" x14ac:dyDescent="0.25">
@@ -16685,7 +16717,7 @@
         <v>38</v>
       </c>
       <c r="F554">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G554" t="s">
         <v>37</v>
@@ -16714,7 +16746,7 @@
         <v>38</v>
       </c>
       <c r="F555">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G555" t="s">
         <v>37</v>
@@ -16743,7 +16775,7 @@
         <v>38</v>
       </c>
       <c r="F556">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G556" t="s">
         <v>37</v>
@@ -16755,7 +16787,7 @@
         <v>19</v>
       </c>
       <c r="J556" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="557" spans="2:10" x14ac:dyDescent="0.25">
@@ -16772,7 +16804,7 @@
         <v>38</v>
       </c>
       <c r="F557">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G557" t="s">
         <v>37</v>
@@ -16801,7 +16833,7 @@
         <v>38</v>
       </c>
       <c r="F558">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G558" t="s">
         <v>37</v>
@@ -16810,10 +16842,10 @@
         <v>17</v>
       </c>
       <c r="I558" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J558" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="559" spans="2:10" x14ac:dyDescent="0.25">
@@ -16830,7 +16862,7 @@
         <v>38</v>
       </c>
       <c r="F559">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G559" t="s">
         <v>37</v>
@@ -16859,7 +16891,7 @@
         <v>38</v>
       </c>
       <c r="F560">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G560" t="s">
         <v>37</v>
@@ -16888,7 +16920,7 @@
         <v>38</v>
       </c>
       <c r="F561">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G561" t="s">
         <v>37</v>
@@ -16900,7 +16932,7 @@
         <v>21</v>
       </c>
       <c r="J561" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="562" spans="2:10" x14ac:dyDescent="0.25">
@@ -16917,7 +16949,7 @@
         <v>38</v>
       </c>
       <c r="F562">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G562" t="s">
         <v>37</v>
@@ -16946,7 +16978,7 @@
         <v>38</v>
       </c>
       <c r="F563">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G563" t="s">
         <v>37</v>
@@ -16955,10 +16987,10 @@
         <v>17</v>
       </c>
       <c r="I563" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J563" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="564" spans="2:10" x14ac:dyDescent="0.25">
@@ -16975,7 +17007,7 @@
         <v>38</v>
       </c>
       <c r="F564">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G564" t="s">
         <v>37</v>
@@ -17004,7 +17036,7 @@
         <v>38</v>
       </c>
       <c r="F565">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G565" t="s">
         <v>37</v>
@@ -17033,7 +17065,7 @@
         <v>38</v>
       </c>
       <c r="F566">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G566" t="s">
         <v>37</v>
@@ -17045,7 +17077,7 @@
         <v>24</v>
       </c>
       <c r="J566" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="567" spans="2:10" x14ac:dyDescent="0.25">
@@ -17062,7 +17094,7 @@
         <v>38</v>
       </c>
       <c r="F567">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G567" t="s">
         <v>37</v>
@@ -17091,7 +17123,7 @@
         <v>38</v>
       </c>
       <c r="F568">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G568" t="s">
         <v>37</v>
@@ -17100,10 +17132,10 @@
         <v>17</v>
       </c>
       <c r="I568" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J568" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="569" spans="2:10" x14ac:dyDescent="0.25">
@@ -17120,7 +17152,7 @@
         <v>38</v>
       </c>
       <c r="F569">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G569" t="s">
         <v>37</v>
@@ -17149,7 +17181,7 @@
         <v>38</v>
       </c>
       <c r="F570">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G570" t="s">
         <v>37</v>
@@ -17178,7 +17210,7 @@
         <v>38</v>
       </c>
       <c r="F571">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G571" t="s">
         <v>37</v>
@@ -17190,7 +17222,7 @@
         <v>25</v>
       </c>
       <c r="J571" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="572" spans="2:10" x14ac:dyDescent="0.25">
@@ -17207,7 +17239,7 @@
         <v>38</v>
       </c>
       <c r="F572">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G572" t="s">
         <v>37</v>
@@ -17230,13 +17262,13 @@
         <v>33</v>
       </c>
       <c r="D573" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E573" t="s">
         <v>38</v>
       </c>
       <c r="F573">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G573" t="s">
         <v>37</v>
@@ -17245,10 +17277,10 @@
         <v>17</v>
       </c>
       <c r="I573" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J573" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="574" spans="2:10" x14ac:dyDescent="0.25">
@@ -17265,7 +17297,7 @@
         <v>38</v>
       </c>
       <c r="F574">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G574" t="s">
         <v>37</v>
@@ -17294,7 +17326,7 @@
         <v>38</v>
       </c>
       <c r="F575">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G575" t="s">
         <v>37</v>
@@ -17323,7 +17355,7 @@
         <v>38</v>
       </c>
       <c r="F576">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G576" t="s">
         <v>37</v>
@@ -17335,7 +17367,7 @@
         <v>19</v>
       </c>
       <c r="J576" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="577" spans="2:10" x14ac:dyDescent="0.25">
@@ -17352,7 +17384,7 @@
         <v>38</v>
       </c>
       <c r="F577">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G577" t="s">
         <v>37</v>
@@ -17381,7 +17413,7 @@
         <v>38</v>
       </c>
       <c r="F578">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G578" t="s">
         <v>37</v>
@@ -17390,10 +17422,10 @@
         <v>17</v>
       </c>
       <c r="I578" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J578" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="579" spans="2:10" x14ac:dyDescent="0.25">
@@ -17410,7 +17442,7 @@
         <v>38</v>
       </c>
       <c r="F579">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G579" t="s">
         <v>37</v>
@@ -17439,7 +17471,7 @@
         <v>38</v>
       </c>
       <c r="F580">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G580" t="s">
         <v>37</v>
@@ -17468,7 +17500,7 @@
         <v>38</v>
       </c>
       <c r="F581">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G581" t="s">
         <v>37</v>
@@ -17480,7 +17512,7 @@
         <v>21</v>
       </c>
       <c r="J581" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="582" spans="2:10" x14ac:dyDescent="0.25">
@@ -17497,7 +17529,7 @@
         <v>38</v>
       </c>
       <c r="F582">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G582" t="s">
         <v>37</v>
@@ -17526,7 +17558,7 @@
         <v>38</v>
       </c>
       <c r="F583">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G583" t="s">
         <v>37</v>
@@ -17535,10 +17567,10 @@
         <v>17</v>
       </c>
       <c r="I583" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J583" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="584" spans="2:10" x14ac:dyDescent="0.25">
@@ -17555,7 +17587,7 @@
         <v>38</v>
       </c>
       <c r="F584">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G584" t="s">
         <v>37</v>
@@ -17584,7 +17616,7 @@
         <v>38</v>
       </c>
       <c r="F585">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G585" t="s">
         <v>37</v>
@@ -17613,7 +17645,7 @@
         <v>38</v>
       </c>
       <c r="F586">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G586" t="s">
         <v>37</v>
@@ -17625,7 +17657,7 @@
         <v>24</v>
       </c>
       <c r="J586" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="587" spans="2:10" x14ac:dyDescent="0.25">
@@ -17642,7 +17674,7 @@
         <v>38</v>
       </c>
       <c r="F587">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G587" t="s">
         <v>37</v>
@@ -17671,7 +17703,7 @@
         <v>38</v>
       </c>
       <c r="F588">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G588" t="s">
         <v>37</v>
@@ -17680,10 +17712,10 @@
         <v>17</v>
       </c>
       <c r="I588" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J588" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="589" spans="2:10" x14ac:dyDescent="0.25">
@@ -17700,7 +17732,7 @@
         <v>38</v>
       </c>
       <c r="F589">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G589" t="s">
         <v>37</v>
@@ -17729,7 +17761,7 @@
         <v>38</v>
       </c>
       <c r="F590">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G590" t="s">
         <v>37</v>
@@ -17758,7 +17790,7 @@
         <v>38</v>
       </c>
       <c r="F591">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G591" t="s">
         <v>37</v>
@@ -17770,7 +17802,7 @@
         <v>25</v>
       </c>
       <c r="J591" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="592" spans="2:10" x14ac:dyDescent="0.25">
@@ -17787,7 +17819,7 @@
         <v>38</v>
       </c>
       <c r="F592">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G592" t="s">
         <v>37</v>
@@ -17807,16 +17839,16 @@
         <v>14</v>
       </c>
       <c r="C593" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D593" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E593" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F593">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G593" t="s">
         <v>37</v>
@@ -17825,10 +17857,10 @@
         <v>17</v>
       </c>
       <c r="I593" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J593" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="594" spans="2:10" x14ac:dyDescent="0.25">
@@ -17845,7 +17877,7 @@
         <v>17</v>
       </c>
       <c r="F594">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G594" t="s">
         <v>37</v>
@@ -17874,7 +17906,7 @@
         <v>17</v>
       </c>
       <c r="F595">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G595" t="s">
         <v>37</v>
@@ -17903,7 +17935,7 @@
         <v>17</v>
       </c>
       <c r="F596">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G596" t="s">
         <v>37</v>
@@ -17915,7 +17947,7 @@
         <v>19</v>
       </c>
       <c r="J596" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="597" spans="2:10" x14ac:dyDescent="0.25">
@@ -17932,7 +17964,7 @@
         <v>17</v>
       </c>
       <c r="F597">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G597" t="s">
         <v>37</v>
@@ -17961,7 +17993,7 @@
         <v>17</v>
       </c>
       <c r="F598">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G598" t="s">
         <v>37</v>
@@ -17970,10 +18002,10 @@
         <v>17</v>
       </c>
       <c r="I598" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J598" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="599" spans="2:10" x14ac:dyDescent="0.25">
@@ -17990,7 +18022,7 @@
         <v>17</v>
       </c>
       <c r="F599">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G599" t="s">
         <v>37</v>
@@ -18019,7 +18051,7 @@
         <v>17</v>
       </c>
       <c r="F600">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G600" t="s">
         <v>37</v>
@@ -18048,7 +18080,7 @@
         <v>17</v>
       </c>
       <c r="F601">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G601" t="s">
         <v>37</v>
@@ -18060,7 +18092,7 @@
         <v>21</v>
       </c>
       <c r="J601" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="602" spans="2:10" x14ac:dyDescent="0.25">
@@ -18077,7 +18109,7 @@
         <v>17</v>
       </c>
       <c r="F602">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G602" t="s">
         <v>37</v>
@@ -18106,7 +18138,7 @@
         <v>17</v>
       </c>
       <c r="F603">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G603" t="s">
         <v>37</v>
@@ -18115,10 +18147,10 @@
         <v>17</v>
       </c>
       <c r="I603" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J603" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="604" spans="2:10" x14ac:dyDescent="0.25">
@@ -18135,7 +18167,7 @@
         <v>17</v>
       </c>
       <c r="F604">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G604" t="s">
         <v>37</v>
@@ -18164,7 +18196,7 @@
         <v>17</v>
       </c>
       <c r="F605">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G605" t="s">
         <v>37</v>
@@ -18193,7 +18225,7 @@
         <v>17</v>
       </c>
       <c r="F606">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G606" t="s">
         <v>37</v>
@@ -18205,7 +18237,7 @@
         <v>24</v>
       </c>
       <c r="J606" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="607" spans="2:10" x14ac:dyDescent="0.25">
@@ -18222,7 +18254,7 @@
         <v>17</v>
       </c>
       <c r="F607">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G607" t="s">
         <v>37</v>
@@ -18251,7 +18283,7 @@
         <v>17</v>
       </c>
       <c r="F608">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G608" t="s">
         <v>37</v>
@@ -18260,10 +18292,10 @@
         <v>17</v>
       </c>
       <c r="I608" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J608" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="609" spans="2:10" x14ac:dyDescent="0.25">
@@ -18280,7 +18312,7 @@
         <v>17</v>
       </c>
       <c r="F609">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G609" t="s">
         <v>37</v>
@@ -18309,7 +18341,7 @@
         <v>17</v>
       </c>
       <c r="F610">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G610" t="s">
         <v>37</v>
@@ -18338,7 +18370,7 @@
         <v>17</v>
       </c>
       <c r="F611">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G611" t="s">
         <v>37</v>
@@ -18350,7 +18382,7 @@
         <v>25</v>
       </c>
       <c r="J611" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="612" spans="2:10" x14ac:dyDescent="0.25">
@@ -18367,7 +18399,7 @@
         <v>17</v>
       </c>
       <c r="F612">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G612" t="s">
         <v>37</v>
@@ -18390,13 +18422,13 @@
         <v>35</v>
       </c>
       <c r="D613" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E613" t="s">
         <v>17</v>
       </c>
       <c r="F613">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G613" t="s">
         <v>37</v>
@@ -18405,10 +18437,10 @@
         <v>17</v>
       </c>
       <c r="I613" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J613" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="614" spans="2:10" x14ac:dyDescent="0.25">
@@ -18425,7 +18457,7 @@
         <v>17</v>
       </c>
       <c r="F614">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G614" t="s">
         <v>37</v>
@@ -18454,7 +18486,7 @@
         <v>17</v>
       </c>
       <c r="F615">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G615" t="s">
         <v>37</v>
@@ -18483,7 +18515,7 @@
         <v>17</v>
       </c>
       <c r="F616">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G616" t="s">
         <v>37</v>
@@ -18495,7 +18527,7 @@
         <v>19</v>
       </c>
       <c r="J616" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="617" spans="2:10" x14ac:dyDescent="0.25">
@@ -18512,7 +18544,7 @@
         <v>17</v>
       </c>
       <c r="F617">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G617" t="s">
         <v>37</v>
@@ -18541,7 +18573,7 @@
         <v>17</v>
       </c>
       <c r="F618">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G618" t="s">
         <v>37</v>
@@ -18550,10 +18582,10 @@
         <v>17</v>
       </c>
       <c r="I618" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J618" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="619" spans="2:10" x14ac:dyDescent="0.25">
@@ -18570,7 +18602,7 @@
         <v>17</v>
       </c>
       <c r="F619">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G619" t="s">
         <v>37</v>
@@ -18599,7 +18631,7 @@
         <v>17</v>
       </c>
       <c r="F620">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G620" t="s">
         <v>37</v>
@@ -18628,7 +18660,7 @@
         <v>17</v>
       </c>
       <c r="F621">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G621" t="s">
         <v>37</v>
@@ -18640,7 +18672,7 @@
         <v>21</v>
       </c>
       <c r="J621" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="622" spans="2:10" x14ac:dyDescent="0.25">
@@ -18657,7 +18689,7 @@
         <v>17</v>
       </c>
       <c r="F622">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G622" t="s">
         <v>37</v>
@@ -18686,7 +18718,7 @@
         <v>17</v>
       </c>
       <c r="F623">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G623" t="s">
         <v>37</v>
@@ -18695,10 +18727,10 @@
         <v>17</v>
       </c>
       <c r="I623" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J623" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="624" spans="2:10" x14ac:dyDescent="0.25">
@@ -18715,7 +18747,7 @@
         <v>17</v>
       </c>
       <c r="F624">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G624" t="s">
         <v>37</v>
@@ -18744,7 +18776,7 @@
         <v>17</v>
       </c>
       <c r="F625">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G625" t="s">
         <v>37</v>
@@ -18773,7 +18805,7 @@
         <v>17</v>
       </c>
       <c r="F626">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G626" t="s">
         <v>37</v>
@@ -18785,7 +18817,7 @@
         <v>24</v>
       </c>
       <c r="J626" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="627" spans="2:10" x14ac:dyDescent="0.25">
@@ -18802,7 +18834,7 @@
         <v>17</v>
       </c>
       <c r="F627">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G627" t="s">
         <v>37</v>
@@ -18831,7 +18863,7 @@
         <v>17</v>
       </c>
       <c r="F628">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G628" t="s">
         <v>37</v>
@@ -18840,10 +18872,10 @@
         <v>17</v>
       </c>
       <c r="I628" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J628" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="629" spans="2:10" x14ac:dyDescent="0.25">
@@ -18860,7 +18892,7 @@
         <v>17</v>
       </c>
       <c r="F629">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G629" t="s">
         <v>37</v>
@@ -18889,7 +18921,7 @@
         <v>17</v>
       </c>
       <c r="F630">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G630" t="s">
         <v>37</v>
@@ -18918,7 +18950,7 @@
         <v>17</v>
       </c>
       <c r="F631">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G631" t="s">
         <v>37</v>
@@ -18930,7 +18962,7 @@
         <v>25</v>
       </c>
       <c r="J631" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="632" spans="2:10" x14ac:dyDescent="0.25">
@@ -18947,7 +18979,7 @@
         <v>17</v>
       </c>
       <c r="F632">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G632" t="s">
         <v>37</v>
@@ -18970,13 +19002,13 @@
         <v>35</v>
       </c>
       <c r="D633" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E633" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F633">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G633" t="s">
         <v>37</v>
@@ -18985,10 +19017,10 @@
         <v>17</v>
       </c>
       <c r="I633" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J633" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="634" spans="2:10" x14ac:dyDescent="0.25">
@@ -19005,7 +19037,7 @@
         <v>38</v>
       </c>
       <c r="F634">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G634" t="s">
         <v>37</v>
@@ -19034,7 +19066,7 @@
         <v>38</v>
       </c>
       <c r="F635">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G635" t="s">
         <v>37</v>
@@ -19063,7 +19095,7 @@
         <v>38</v>
       </c>
       <c r="F636">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G636" t="s">
         <v>37</v>
@@ -19075,7 +19107,7 @@
         <v>19</v>
       </c>
       <c r="J636" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="637" spans="2:10" x14ac:dyDescent="0.25">
@@ -19092,7 +19124,7 @@
         <v>38</v>
       </c>
       <c r="F637">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G637" t="s">
         <v>37</v>
@@ -19121,7 +19153,7 @@
         <v>38</v>
       </c>
       <c r="F638">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G638" t="s">
         <v>37</v>
@@ -19130,10 +19162,10 @@
         <v>17</v>
       </c>
       <c r="I638" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J638" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="639" spans="2:10" x14ac:dyDescent="0.25">
@@ -19150,7 +19182,7 @@
         <v>38</v>
       </c>
       <c r="F639">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G639" t="s">
         <v>37</v>
@@ -19179,7 +19211,7 @@
         <v>38</v>
       </c>
       <c r="F640">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G640" t="s">
         <v>37</v>
@@ -19208,7 +19240,7 @@
         <v>38</v>
       </c>
       <c r="F641">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G641" t="s">
         <v>37</v>
@@ -19220,7 +19252,7 @@
         <v>21</v>
       </c>
       <c r="J641" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="642" spans="2:10" x14ac:dyDescent="0.25">
@@ -19237,7 +19269,7 @@
         <v>38</v>
       </c>
       <c r="F642">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G642" t="s">
         <v>37</v>
@@ -19266,7 +19298,7 @@
         <v>38</v>
       </c>
       <c r="F643">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G643" t="s">
         <v>37</v>
@@ -19275,10 +19307,10 @@
         <v>17</v>
       </c>
       <c r="I643" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J643" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="644" spans="2:10" x14ac:dyDescent="0.25">
@@ -19295,7 +19327,7 @@
         <v>38</v>
       </c>
       <c r="F644">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G644" t="s">
         <v>37</v>
@@ -19324,7 +19356,7 @@
         <v>38</v>
       </c>
       <c r="F645">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G645" t="s">
         <v>37</v>
@@ -19353,7 +19385,7 @@
         <v>38</v>
       </c>
       <c r="F646">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G646" t="s">
         <v>37</v>
@@ -19365,7 +19397,7 @@
         <v>24</v>
       </c>
       <c r="J646" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="647" spans="2:10" x14ac:dyDescent="0.25">
@@ -19382,7 +19414,7 @@
         <v>38</v>
       </c>
       <c r="F647">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G647" t="s">
         <v>37</v>
@@ -19411,7 +19443,7 @@
         <v>38</v>
       </c>
       <c r="F648">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G648" t="s">
         <v>37</v>
@@ -19420,10 +19452,10 @@
         <v>17</v>
       </c>
       <c r="I648" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J648" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="649" spans="2:10" x14ac:dyDescent="0.25">
@@ -19440,7 +19472,7 @@
         <v>38</v>
       </c>
       <c r="F649">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G649" t="s">
         <v>37</v>
@@ -19469,7 +19501,7 @@
         <v>38</v>
       </c>
       <c r="F650">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G650" t="s">
         <v>37</v>
@@ -19498,7 +19530,7 @@
         <v>38</v>
       </c>
       <c r="F651">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G651" t="s">
         <v>37</v>
@@ -19510,7 +19542,7 @@
         <v>25</v>
       </c>
       <c r="J651" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="652" spans="2:10" x14ac:dyDescent="0.25">
@@ -19527,7 +19559,7 @@
         <v>38</v>
       </c>
       <c r="F652">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G652" t="s">
         <v>37</v>
@@ -19550,13 +19582,13 @@
         <v>35</v>
       </c>
       <c r="D653" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E653" t="s">
         <v>38</v>
       </c>
       <c r="F653">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G653" t="s">
         <v>37</v>
@@ -19565,10 +19597,10 @@
         <v>17</v>
       </c>
       <c r="I653" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J653" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="654" spans="2:10" x14ac:dyDescent="0.25">
@@ -19585,7 +19617,7 @@
         <v>38</v>
       </c>
       <c r="F654">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G654" t="s">
         <v>37</v>
@@ -19614,7 +19646,7 @@
         <v>38</v>
       </c>
       <c r="F655">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G655" t="s">
         <v>37</v>
@@ -19643,7 +19675,7 @@
         <v>38</v>
       </c>
       <c r="F656">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G656" t="s">
         <v>37</v>
@@ -19655,7 +19687,7 @@
         <v>19</v>
       </c>
       <c r="J656" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="657" spans="2:10" x14ac:dyDescent="0.25">
@@ -19672,7 +19704,7 @@
         <v>38</v>
       </c>
       <c r="F657">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G657" t="s">
         <v>37</v>
@@ -19701,7 +19733,7 @@
         <v>38</v>
       </c>
       <c r="F658">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G658" t="s">
         <v>37</v>
@@ -19710,10 +19742,10 @@
         <v>17</v>
       </c>
       <c r="I658" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J658" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="659" spans="2:10" x14ac:dyDescent="0.25">
@@ -19730,7 +19762,7 @@
         <v>38</v>
       </c>
       <c r="F659">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G659" t="s">
         <v>37</v>
@@ -19759,7 +19791,7 @@
         <v>38</v>
       </c>
       <c r="F660">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G660" t="s">
         <v>37</v>
@@ -19788,7 +19820,7 @@
         <v>38</v>
       </c>
       <c r="F661">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G661" t="s">
         <v>37</v>
@@ -19800,7 +19832,7 @@
         <v>21</v>
       </c>
       <c r="J661" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="662" spans="2:10" x14ac:dyDescent="0.25">
@@ -19817,7 +19849,7 @@
         <v>38</v>
       </c>
       <c r="F662">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G662" t="s">
         <v>37</v>
@@ -19846,7 +19878,7 @@
         <v>38</v>
       </c>
       <c r="F663">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G663" t="s">
         <v>37</v>
@@ -19855,10 +19887,10 @@
         <v>17</v>
       </c>
       <c r="I663" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J663" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="664" spans="2:10" x14ac:dyDescent="0.25">
@@ -19875,7 +19907,7 @@
         <v>38</v>
       </c>
       <c r="F664">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G664" t="s">
         <v>37</v>
@@ -19904,7 +19936,7 @@
         <v>38</v>
       </c>
       <c r="F665">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G665" t="s">
         <v>37</v>
@@ -19933,7 +19965,7 @@
         <v>38</v>
       </c>
       <c r="F666">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G666" t="s">
         <v>37</v>
@@ -19945,7 +19977,7 @@
         <v>24</v>
       </c>
       <c r="J666" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="667" spans="2:10" x14ac:dyDescent="0.25">
@@ -19962,7 +19994,7 @@
         <v>38</v>
       </c>
       <c r="F667">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G667" t="s">
         <v>37</v>
@@ -19991,7 +20023,7 @@
         <v>38</v>
       </c>
       <c r="F668">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G668" t="s">
         <v>37</v>
@@ -20000,10 +20032,10 @@
         <v>17</v>
       </c>
       <c r="I668" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J668" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="669" spans="2:10" x14ac:dyDescent="0.25">
@@ -20020,7 +20052,7 @@
         <v>38</v>
       </c>
       <c r="F669">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G669" t="s">
         <v>37</v>
@@ -20049,7 +20081,7 @@
         <v>38</v>
       </c>
       <c r="F670">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G670" t="s">
         <v>37</v>
@@ -20078,7 +20110,7 @@
         <v>38</v>
       </c>
       <c r="F671">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G671" t="s">
         <v>37</v>
@@ -20090,7 +20122,7 @@
         <v>25</v>
       </c>
       <c r="J671" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="672" spans="2:10" x14ac:dyDescent="0.25">
@@ -20107,7 +20139,7 @@
         <v>38</v>
       </c>
       <c r="F672">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G672" t="s">
         <v>37</v>
@@ -20127,28 +20159,28 @@
         <v>14</v>
       </c>
       <c r="C673" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D673" t="s">
         <v>26</v>
       </c>
       <c r="E673" t="s">
-        <v>17</v>
-      </c>
-      <c r="F673" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="F673">
+        <v>12</v>
       </c>
       <c r="G673" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H673" t="s">
         <v>17</v>
       </c>
       <c r="I673" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J673" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="674" spans="2:10" x14ac:dyDescent="0.25">
@@ -20159,7 +20191,7 @@
         <v>30</v>
       </c>
       <c r="D674" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E674" t="s">
         <v>17</v>
@@ -20174,10 +20206,10 @@
         <v>17</v>
       </c>
       <c r="I674" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J674" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="675" spans="2:10" x14ac:dyDescent="0.25">
@@ -20203,7 +20235,7 @@
         <v>17</v>
       </c>
       <c r="I675" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J675" t="s">
         <v>28</v>
@@ -20232,7 +20264,7 @@
         <v>17</v>
       </c>
       <c r="I676" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J676" t="s">
         <v>28</v>
@@ -20246,7 +20278,7 @@
         <v>30</v>
       </c>
       <c r="D677" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E677" t="s">
         <v>17</v>
@@ -20261,10 +20293,10 @@
         <v>17</v>
       </c>
       <c r="I677" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J677" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="678" spans="2:10" x14ac:dyDescent="0.25">
@@ -20290,7 +20322,7 @@
         <v>17</v>
       </c>
       <c r="I678" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J678" t="s">
         <v>23</v>
@@ -20319,7 +20351,7 @@
         <v>17</v>
       </c>
       <c r="I679" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J679" t="s">
         <v>23</v>
@@ -20333,7 +20365,7 @@
         <v>30</v>
       </c>
       <c r="D680" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E680" t="s">
         <v>17</v>
@@ -20348,10 +20380,10 @@
         <v>17</v>
       </c>
       <c r="I680" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J680" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="681" spans="2:10" x14ac:dyDescent="0.25">
@@ -20362,7 +20394,7 @@
         <v>30</v>
       </c>
       <c r="D681" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E681" t="s">
         <v>17</v>
@@ -20377,10 +20409,10 @@
         <v>17</v>
       </c>
       <c r="I681" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J681" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="682" spans="2:10" x14ac:dyDescent="0.25">
@@ -20406,7 +20438,7 @@
         <v>17</v>
       </c>
       <c r="I682" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J682" t="s">
         <v>28</v>
@@ -20435,7 +20467,7 @@
         <v>17</v>
       </c>
       <c r="I683" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J683" t="s">
         <v>28</v>
@@ -20449,7 +20481,7 @@
         <v>30</v>
       </c>
       <c r="D684" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E684" t="s">
         <v>17</v>
@@ -20464,10 +20496,10 @@
         <v>17</v>
       </c>
       <c r="I684" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J684" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="685" spans="2:10" x14ac:dyDescent="0.25">
@@ -20493,7 +20525,7 @@
         <v>17</v>
       </c>
       <c r="I685" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J685" t="s">
         <v>23</v>
@@ -20522,7 +20554,7 @@
         <v>17</v>
       </c>
       <c r="I686" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J686" t="s">
         <v>23</v>
@@ -20536,7 +20568,7 @@
         <v>30</v>
       </c>
       <c r="D687" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E687" t="s">
         <v>17</v>
@@ -20545,16 +20577,16 @@
         <v>39</v>
       </c>
       <c r="G687" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H687" t="s">
         <v>17</v>
       </c>
       <c r="I687" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J687" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="688" spans="2:10" x14ac:dyDescent="0.25">
@@ -20565,7 +20597,7 @@
         <v>30</v>
       </c>
       <c r="D688" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E688" t="s">
         <v>17</v>
@@ -20580,10 +20612,10 @@
         <v>17</v>
       </c>
       <c r="I688" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J688" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="689" spans="2:10" x14ac:dyDescent="0.25">
@@ -20609,7 +20641,7 @@
         <v>17</v>
       </c>
       <c r="I689" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J689" t="s">
         <v>28</v>
@@ -20638,7 +20670,7 @@
         <v>17</v>
       </c>
       <c r="I690" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J690" t="s">
         <v>28</v>
@@ -20652,7 +20684,7 @@
         <v>30</v>
       </c>
       <c r="D691" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E691" t="s">
         <v>17</v>
@@ -20667,10 +20699,10 @@
         <v>17</v>
       </c>
       <c r="I691" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J691" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="692" spans="2:10" x14ac:dyDescent="0.25">
@@ -20696,7 +20728,7 @@
         <v>17</v>
       </c>
       <c r="I692" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J692" t="s">
         <v>23</v>
@@ -20725,7 +20757,7 @@
         <v>17</v>
       </c>
       <c r="I693" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J693" t="s">
         <v>23</v>
@@ -20739,7 +20771,7 @@
         <v>30</v>
       </c>
       <c r="D694" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E694" t="s">
         <v>17</v>
@@ -20754,10 +20786,10 @@
         <v>17</v>
       </c>
       <c r="I694" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J694" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="695" spans="2:10" x14ac:dyDescent="0.25">
@@ -20768,7 +20800,7 @@
         <v>30</v>
       </c>
       <c r="D695" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E695" t="s">
         <v>17</v>
@@ -20783,10 +20815,10 @@
         <v>17</v>
       </c>
       <c r="I695" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J695" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="696" spans="2:10" x14ac:dyDescent="0.25">
@@ -20812,7 +20844,7 @@
         <v>17</v>
       </c>
       <c r="I696" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J696" t="s">
         <v>28</v>
@@ -20841,7 +20873,7 @@
         <v>17</v>
       </c>
       <c r="I697" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J697" t="s">
         <v>28</v>
@@ -20855,7 +20887,7 @@
         <v>30</v>
       </c>
       <c r="D698" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E698" t="s">
         <v>17</v>
@@ -20870,10 +20902,10 @@
         <v>17</v>
       </c>
       <c r="I698" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J698" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="699" spans="2:10" x14ac:dyDescent="0.25">
@@ -20899,7 +20931,7 @@
         <v>17</v>
       </c>
       <c r="I699" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J699" t="s">
         <v>23</v>
@@ -20928,7 +20960,7 @@
         <v>17</v>
       </c>
       <c r="I700" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J700" t="s">
         <v>23</v>
@@ -20938,9 +20970,38 @@
       <c r="B701" t="s">
         <v>14</v>
       </c>
+      <c r="C701" t="s">
+        <v>30</v>
+      </c>
+      <c r="D701" t="s">
+        <v>29</v>
+      </c>
+      <c r="E701" t="s">
+        <v>17</v>
+      </c>
+      <c r="F701" t="s">
+        <v>39</v>
+      </c>
+      <c r="G701" t="s">
+        <v>41</v>
+      </c>
+      <c r="H701" t="s">
+        <v>17</v>
+      </c>
+      <c r="I701" t="s">
+        <v>24</v>
+      </c>
+      <c r="J701" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="702" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B702" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="703" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B703" t="s">
         <v>14</v>
       </c>
     </row>
